--- a/MRNA.xlsx
+++ b/MRNA.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Martin Shkreli - DL\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12219747-9B5D-4D96-A357-2625219F7961}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A27921B2-4AE3-4E0A-8CF1-BE44D7CB35A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10430" yWindow="3830" windowWidth="22990" windowHeight="13690" activeTab="1" xr2:uid="{57C30761-CAF2-4DE9-93D4-20A7306FD955}"/>
+    <workbookView xWindow="13390" yWindow="3330" windowWidth="22360" windowHeight="16580" activeTab="1" xr2:uid="{57C30761-CAF2-4DE9-93D4-20A7306FD955}"/>
   </bookViews>
   <sheets>
     <sheet name="Master" sheetId="5" r:id="rId1"/>
@@ -46,7 +46,7 @@
     <author>tc={8F36830E-5A19-46F9-85C3-8F6136215DC4}</author>
   </authors>
   <commentList>
-    <comment ref="AE11" authorId="0" shapeId="0" xr:uid="{7A88566D-7393-4EDB-9417-9FF15ED60EED}">
+    <comment ref="AI11" authorId="0" shapeId="0" xr:uid="{7A88566D-7393-4EDB-9417-9FF15ED60EED}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -55,7 +55,7 @@
 Q322 guidance: 18-19B</t>
       </text>
     </comment>
-    <comment ref="AH14" authorId="1" shapeId="0" xr:uid="{8F36830E-5A19-46F9-85C3-8F6136215DC4}">
+    <comment ref="AL14" authorId="1" shapeId="0" xr:uid="{8F36830E-5A19-46F9-85C3-8F6136215DC4}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="167">
   <si>
     <t>Price</t>
   </si>
@@ -526,9 +526,6 @@
     <t>Phase III - data in 2025</t>
   </si>
   <si>
-    <t>mRNA-1283</t>
-  </si>
-  <si>
     <t>Filed/III</t>
   </si>
   <si>
@@ -551,6 +548,27 @@
   </si>
   <si>
     <t>Share</t>
+  </si>
+  <si>
+    <t>Q126</t>
+  </si>
+  <si>
+    <t>Q226</t>
+  </si>
+  <si>
+    <t>Q326</t>
+  </si>
+  <si>
+    <t>Q426</t>
+  </si>
+  <si>
+    <t>II - results 2026</t>
+  </si>
+  <si>
+    <t>8/5/26 PDUFA</t>
+  </si>
+  <si>
+    <t>mNEXSPIKE (mRNA-1283)</t>
   </si>
 </sst>
 </file>
@@ -732,7 +750,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -783,17 +801,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -820,16 +833,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>22</xdr:col>
+      <xdr:col>27</xdr:col>
       <xdr:colOff>21718</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>41604</xdr:rowOff>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>22</xdr:col>
+      <xdr:col>27</xdr:col>
       <xdr:colOff>21718</xdr:colOff>
       <xdr:row>52</xdr:row>
-      <xdr:rowOff>157357</xdr:rowOff>
+      <xdr:rowOff>115753</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -844,8 +857,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="13834063" y="41604"/>
-          <a:ext cx="0" cy="8331339"/>
+          <a:off x="16912718" y="0"/>
+          <a:ext cx="0" cy="8507522"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -870,13 +883,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>33</xdr:col>
+      <xdr:col>37</xdr:col>
       <xdr:colOff>33721</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>4379</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>33</xdr:col>
+      <xdr:col>37</xdr:col>
       <xdr:colOff>33721</xdr:colOff>
       <xdr:row>71</xdr:row>
       <xdr:rowOff>102577</xdr:rowOff>
@@ -1224,11 +1237,11 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="AE11" dT="2022-09-10T06:51:40.15" personId="{7F1476AF-D443-4543-BE7B-E432FEBB72DB}" id="{7A88566D-7393-4EDB-9417-9FF15ED60EED}">
+  <threadedComment ref="AI11" dT="2022-09-10T06:51:40.15" personId="{7F1476AF-D443-4543-BE7B-E432FEBB72DB}" id="{7A88566D-7393-4EDB-9417-9FF15ED60EED}">
     <text>Q222 guidance: Reiterates 21B expected delivery
 Q322 guidance: 18-19B</text>
   </threadedComment>
-  <threadedComment ref="AH14" dT="2025-02-19T17:24:24.34" personId="{7F1476AF-D443-4543-BE7B-E432FEBB72DB}" id="{8F36830E-5A19-46F9-85C3-8F6136215DC4}">
+  <threadedComment ref="AL14" dT="2025-02-19T17:24:24.34" personId="{7F1476AF-D443-4543-BE7B-E432FEBB72DB}" id="{8F36830E-5A19-46F9-85C3-8F6136215DC4}">
     <text>Q424: guidance of 1.5-2.5B</text>
   </threadedComment>
 </ThreadedComments>
@@ -1327,7 +1340,7 @@
         <v>0</v>
       </c>
       <c r="K2" s="20">
-        <v>35</v>
+        <v>81</v>
       </c>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.25">
@@ -1344,21 +1357,15 @@
         <v>1</v>
       </c>
       <c r="K3" s="2">
-        <v>384.81781100000001</v>
+        <v>396.78625899999997</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>125</v>
+        <v>160</v>
       </c>
     </row>
     <row r="4" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B4" s="9" t="s">
-        <v>126</v>
-      </c>
-      <c r="C4" t="s">
-        <v>129</v>
-      </c>
-      <c r="E4" s="15">
-        <v>2024</v>
+        <v>166</v>
       </c>
       <c r="F4" s="15"/>
       <c r="G4" s="15"/>
@@ -1368,141 +1375,137 @@
       </c>
       <c r="K4" s="2">
         <f>+K2*K3</f>
-        <v>13468.623385000001</v>
+        <v>32139.686978999998</v>
       </c>
     </row>
     <row r="5" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B5" s="12"/>
-      <c r="C5" s="13"/>
-      <c r="D5" s="13"/>
-      <c r="E5" s="14" t="s">
-        <v>61</v>
-      </c>
-      <c r="F5" s="14"/>
-      <c r="G5" s="14"/>
-      <c r="H5" s="23"/>
+      <c r="B5" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="C5" t="s">
+        <v>129</v>
+      </c>
+      <c r="E5" s="15">
+        <v>2024</v>
+      </c>
+      <c r="F5" s="15"/>
+      <c r="G5" s="15"/>
+      <c r="H5" s="24"/>
       <c r="J5" t="s">
         <v>3</v>
       </c>
       <c r="K5" s="2">
-        <f>5098+1927+2494</f>
-        <v>9519</v>
+        <f>1908+3297+2251-950</f>
+        <v>6506</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>125</v>
+        <v>160</v>
       </c>
     </row>
     <row r="6" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B6" s="27" t="s">
-        <v>73</v>
-      </c>
-      <c r="C6" s="28" t="s">
-        <v>74</v>
-      </c>
-      <c r="D6" s="28"/>
-      <c r="E6" s="29" t="s">
-        <v>130</v>
-      </c>
-      <c r="F6" s="29"/>
-      <c r="G6" s="29"/>
-      <c r="H6" s="30"/>
+      <c r="B6" s="12"/>
+      <c r="C6" s="13"/>
+      <c r="D6" s="13"/>
+      <c r="E6" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="F6" s="14"/>
+      <c r="G6" s="14"/>
+      <c r="H6" s="23"/>
       <c r="J6" t="s">
         <v>4</v>
       </c>
       <c r="K6" s="2">
-        <v>0</v>
+        <v>590</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>125</v>
+        <v>160</v>
       </c>
     </row>
     <row r="7" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B7" s="9" t="s">
-        <v>152</v>
-      </c>
-      <c r="C7" s="31" t="s">
-        <v>84</v>
-      </c>
-      <c r="D7" s="31"/>
-      <c r="E7" s="32"/>
-      <c r="F7" s="32"/>
-      <c r="G7" s="32"/>
-      <c r="H7" s="24"/>
+      <c r="B7" s="26" t="s">
+        <v>73</v>
+      </c>
+      <c r="C7" s="27" t="s">
+        <v>74</v>
+      </c>
+      <c r="D7" s="27"/>
+      <c r="E7" s="28" t="s">
+        <v>130</v>
+      </c>
+      <c r="F7" s="28"/>
+      <c r="G7" s="28"/>
+      <c r="H7" s="29"/>
       <c r="J7" t="s">
         <v>5</v>
       </c>
       <c r="K7" s="2">
         <f>+K4-K5+K6</f>
-        <v>3949.6233850000008</v>
+        <v>26223.686978999998</v>
       </c>
     </row>
     <row r="8" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B8" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="C8" s="31" t="s">
+      <c r="C8" t="s">
         <v>63</v>
       </c>
-      <c r="D8" s="31"/>
-      <c r="E8" s="32" t="s">
-        <v>103</v>
-      </c>
-      <c r="F8" s="32"/>
-      <c r="G8" s="32"/>
+      <c r="E8" s="15" t="s">
+        <v>165</v>
+      </c>
+      <c r="F8" s="15"/>
+      <c r="G8" s="15"/>
       <c r="H8" s="24"/>
     </row>
     <row r="9" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B9" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="C9" s="31" t="s">
+      <c r="C9" t="s">
         <v>63</v>
       </c>
-      <c r="D9" s="31"/>
-      <c r="E9" s="32"/>
-      <c r="F9" s="32"/>
-      <c r="G9" s="32"/>
+      <c r="E9" s="15"/>
+      <c r="F9" s="15"/>
+      <c r="G9" s="15"/>
       <c r="H9" s="24"/>
     </row>
     <row r="10" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B10" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="C10" s="31" t="s">
+      <c r="C10" t="s">
         <v>63</v>
       </c>
-      <c r="D10" s="31"/>
-      <c r="E10" s="32"/>
-      <c r="F10" s="32"/>
-      <c r="G10" s="32"/>
+      <c r="E10" s="15"/>
+      <c r="F10" s="15"/>
+      <c r="G10" s="15"/>
       <c r="H10" s="24"/>
     </row>
     <row r="11" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B11" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="C11" s="31" t="s">
+      <c r="C11" t="s">
         <v>63</v>
       </c>
-      <c r="D11" s="31"/>
-      <c r="E11" s="32"/>
-      <c r="F11" s="32"/>
-      <c r="G11" s="32"/>
+      <c r="E11" s="15"/>
+      <c r="F11" s="15"/>
+      <c r="G11" s="15"/>
       <c r="H11" s="24"/>
     </row>
     <row r="12" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B12" s="9" t="s">
         <v>140</v>
       </c>
-      <c r="C12" s="31" t="s">
+      <c r="C12" t="s">
         <v>141</v>
       </c>
-      <c r="D12" s="31"/>
-      <c r="E12" s="32" t="s">
-        <v>153</v>
-      </c>
-      <c r="F12" s="32"/>
-      <c r="G12" s="32"/>
+      <c r="E12" s="15" t="s">
+        <v>152</v>
+      </c>
+      <c r="F12" s="15"/>
+      <c r="G12" s="15"/>
       <c r="H12" s="24"/>
       <c r="J12" t="s">
         <v>68</v>
@@ -1512,13 +1515,12 @@
       <c r="B13" s="9" t="s">
         <v>88</v>
       </c>
-      <c r="C13" s="31" t="s">
+      <c r="C13" t="s">
         <v>63</v>
       </c>
-      <c r="D13" s="31"/>
-      <c r="E13" s="32"/>
-      <c r="F13" s="32"/>
-      <c r="G13" s="32"/>
+      <c r="E13" s="15"/>
+      <c r="F13" s="15"/>
+      <c r="G13" s="15"/>
       <c r="H13" s="24"/>
       <c r="J13" t="s">
         <v>75</v>
@@ -1528,32 +1530,31 @@
       <c r="B14" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="C14" s="31" t="s">
+      <c r="C14" t="s">
         <v>65</v>
       </c>
-      <c r="D14" s="31"/>
-      <c r="E14" s="32" t="s">
-        <v>111</v>
-      </c>
-      <c r="F14" s="32"/>
-      <c r="G14" s="32"/>
+      <c r="E14" s="15" t="s">
+        <v>164</v>
+      </c>
+      <c r="F14" s="15"/>
+      <c r="G14" s="15"/>
       <c r="H14" s="24"/>
     </row>
     <row r="15" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B15" s="9" t="s">
         <v>127</v>
       </c>
-      <c r="C15" s="31" t="s">
+      <c r="C15" t="s">
         <v>128</v>
       </c>
-      <c r="D15" s="31" t="s">
+      <c r="D15" t="s">
         <v>147</v>
       </c>
-      <c r="E15" s="32" t="s">
+      <c r="E15" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="F15" s="32"/>
-      <c r="G15" s="32"/>
+      <c r="F15" s="15"/>
+      <c r="G15" s="15"/>
       <c r="H15" s="24"/>
       <c r="J15" t="s">
         <v>99</v>
@@ -1563,45 +1564,43 @@
       <c r="B16" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="C16" s="31" t="s">
+      <c r="C16" t="s">
         <v>70</v>
       </c>
-      <c r="D16" s="31"/>
-      <c r="E16" s="32" t="s">
+      <c r="E16" s="15" t="s">
         <v>148</v>
       </c>
-      <c r="F16" s="32"/>
-      <c r="G16" s="32"/>
+      <c r="F16" s="15"/>
+      <c r="G16" s="15"/>
       <c r="H16" s="24"/>
     </row>
     <row r="17" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B17" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="C17" s="31" t="s">
+      <c r="C17" t="s">
         <v>72</v>
       </c>
-      <c r="D17" s="31"/>
-      <c r="E17" s="32"/>
-      <c r="F17" s="32"/>
-      <c r="G17" s="32"/>
+      <c r="E17" s="15"/>
+      <c r="F17" s="15"/>
+      <c r="G17" s="15"/>
       <c r="H17" s="24"/>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B18" s="22" t="s">
         <v>110</v>
       </c>
-      <c r="C18" s="31" t="s">
+      <c r="C18" t="s">
         <v>109</v>
       </c>
-      <c r="D18" s="31" t="s">
+      <c r="D18" t="s">
         <v>82</v>
       </c>
-      <c r="E18" s="32" t="s">
+      <c r="E18" s="15" t="s">
         <v>111</v>
       </c>
-      <c r="F18" s="32"/>
-      <c r="G18" s="32" t="s">
+      <c r="F18" s="15"/>
+      <c r="G18" s="15" t="s">
         <v>115</v>
       </c>
       <c r="H18" s="24"/>
@@ -1610,26 +1609,24 @@
       <c r="B19" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="C19" s="31" t="s">
+      <c r="C19" t="s">
         <v>90</v>
       </c>
-      <c r="D19" s="31"/>
-      <c r="E19" s="32"/>
-      <c r="F19" s="32"/>
-      <c r="G19" s="32"/>
+      <c r="E19" s="15"/>
+      <c r="F19" s="15"/>
+      <c r="G19" s="15"/>
       <c r="H19" s="24"/>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B20" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="C20" s="31" t="s">
+      <c r="C20" t="s">
         <v>93</v>
       </c>
-      <c r="D20" s="31"/>
-      <c r="E20" s="32"/>
-      <c r="F20" s="32"/>
-      <c r="G20" s="32"/>
+      <c r="E20" s="15"/>
+      <c r="F20" s="15"/>
+      <c r="G20" s="15"/>
       <c r="H20" s="24"/>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
@@ -1708,7 +1705,7 @@
       </c>
     </row>
     <row r="32" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B32" s="26" t="s">
+      <c r="B32" t="s">
         <v>80</v>
       </c>
       <c r="C32" t="s">
@@ -1740,21 +1737,21 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{763993C8-90F0-44F5-B32B-73F90FF84785}">
-  <dimension ref="A1:EI59"/>
+  <dimension ref="A1:EM59"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.1796875" bestFit="1" customWidth="1"/>
     <col min="3" max="14" width="9.1796875" style="1"/>
-    <col min="47" max="47" width="9.54296875" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="9.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A1" s="19" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:48" x14ac:dyDescent="0.25">
       <c r="C2" s="1" t="s">
         <v>9</v>
       </c>
@@ -1827,75 +1824,87 @@
       <c r="Z2" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="AB2">
+      <c r="AA2" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="AB2" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="AC2" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="AD2" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="AF2">
         <v>2019</v>
       </c>
-      <c r="AC2">
-        <f>+AB2+1</f>
+      <c r="AG2">
+        <f>+AF2+1</f>
         <v>2020</v>
       </c>
-      <c r="AD2">
-        <f t="shared" ref="AD2:AI2" si="0">+AC2+1</f>
+      <c r="AH2">
+        <f t="shared" ref="AH2:AM2" si="0">+AG2+1</f>
         <v>2021</v>
       </c>
-      <c r="AE2">
+      <c r="AI2">
         <f t="shared" si="0"/>
         <v>2022</v>
       </c>
-      <c r="AF2">
+      <c r="AJ2">
         <f t="shared" si="0"/>
         <v>2023</v>
       </c>
-      <c r="AG2">
+      <c r="AK2">
         <f t="shared" si="0"/>
         <v>2024</v>
       </c>
-      <c r="AH2">
+      <c r="AL2">
         <f t="shared" si="0"/>
         <v>2025</v>
       </c>
-      <c r="AI2">
+      <c r="AM2">
         <f t="shared" si="0"/>
         <v>2026</v>
       </c>
-      <c r="AJ2">
-        <f>+AI2+1</f>
+      <c r="AN2">
+        <f>+AM2+1</f>
         <v>2027</v>
       </c>
-      <c r="AK2">
-        <f t="shared" ref="AK2:AR2" si="1">+AJ2+1</f>
+      <c r="AO2">
+        <f t="shared" ref="AO2:AV2" si="1">+AN2+1</f>
         <v>2028</v>
       </c>
-      <c r="AL2">
+      <c r="AP2">
         <f t="shared" si="1"/>
         <v>2029</v>
       </c>
-      <c r="AM2">
+      <c r="AQ2">
         <f t="shared" si="1"/>
         <v>2030</v>
       </c>
-      <c r="AN2">
+      <c r="AR2">
         <f t="shared" si="1"/>
         <v>2031</v>
       </c>
-      <c r="AO2">
+      <c r="AS2">
         <f t="shared" si="1"/>
         <v>2032</v>
       </c>
-      <c r="AP2">
+      <c r="AT2">
         <f t="shared" si="1"/>
         <v>2033</v>
       </c>
-      <c r="AQ2">
+      <c r="AU2">
         <f t="shared" si="1"/>
         <v>2034</v>
       </c>
-      <c r="AR2">
+      <c r="AV2">
         <f t="shared" si="1"/>
         <v>2035</v>
       </c>
     </row>
-    <row r="3" spans="1:44" s="7" customFormat="1" ht="13" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:48" s="7" customFormat="1" ht="13" x14ac:dyDescent="0.3">
       <c r="B3" s="7" t="s">
         <v>54</v>
       </c>
@@ -1919,7 +1928,7 @@
       <c r="T3" s="8"/>
       <c r="U3" s="8"/>
     </row>
-    <row r="4" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:48" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>138</v>
       </c>
@@ -1930,15 +1939,15 @@
       <c r="S4" s="1"/>
       <c r="T4" s="1"/>
       <c r="U4" s="1"/>
-      <c r="AF4">
+      <c r="AJ4">
         <v>0</v>
       </c>
-      <c r="AG4" s="2">
+      <c r="AK4" s="2">
         <v>1100</v>
       </c>
-      <c r="AH4" s="2"/>
-    </row>
-    <row r="5" spans="1:44" x14ac:dyDescent="0.25">
+      <c r="AL4" s="2"/>
+    </row>
+    <row r="5" spans="1:48" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>139</v>
       </c>
@@ -1949,12 +1958,12 @@
       <c r="S5" s="1"/>
       <c r="T5" s="1"/>
       <c r="U5" s="1"/>
-      <c r="AG5" s="2">
+      <c r="AK5" s="2">
         <v>1500</v>
       </c>
-      <c r="AH5" s="2"/>
-    </row>
-    <row r="6" spans="1:44" x14ac:dyDescent="0.25">
+      <c r="AL5" s="2"/>
+    </row>
+    <row r="6" spans="1:48" x14ac:dyDescent="0.25">
       <c r="O6" s="1"/>
       <c r="P6" s="1"/>
       <c r="Q6" s="1"/>
@@ -1962,10 +1971,10 @@
       <c r="S6" s="1"/>
       <c r="T6" s="1"/>
       <c r="U6" s="1"/>
-      <c r="AG6" s="2"/>
-      <c r="AH6" s="2"/>
-    </row>
-    <row r="7" spans="1:44" x14ac:dyDescent="0.25">
+      <c r="AK6" s="2"/>
+      <c r="AL6" s="2"/>
+    </row>
+    <row r="7" spans="1:48" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>146</v>
       </c>
@@ -1982,70 +1991,70 @@
         <v>15</v>
       </c>
       <c r="W7">
-        <f>+V7+5</f>
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="X7">
-        <f>+W7+5</f>
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="Y7">
-        <f>+X7+5</f>
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="Z7">
-        <f>+Y7+5</f>
-        <v>35</v>
-      </c>
-      <c r="AG7" s="2">
+        <f>8-Y7-X7-W7</f>
+        <v>4</v>
+      </c>
+      <c r="AA7">
+        <v>7</v>
+      </c>
+      <c r="AK7" s="2">
         <v>50</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AL7" s="2">
         <f>SUM(W7:Z7)</f>
-        <v>110</v>
-      </c>
-      <c r="AI7" s="2">
-        <f>+AH7*1.3</f>
-        <v>143</v>
-      </c>
-      <c r="AJ7" s="2">
-        <f>+AI7*1.3</f>
-        <v>185.9</v>
-      </c>
-      <c r="AK7" s="2">
-        <f>+AJ7*1.3</f>
-        <v>241.67000000000002</v>
-      </c>
-      <c r="AL7" s="2">
-        <f>+AK7*1.1</f>
-        <v>265.83700000000005</v>
+        <v>8</v>
       </c>
       <c r="AM7" s="2">
-        <f>+AL7*1.1</f>
-        <v>292.42070000000007</v>
+        <f>+AL7*1.3</f>
+        <v>10.4</v>
       </c>
       <c r="AN7" s="2">
-        <f>+AM7*1.1</f>
-        <v>321.66277000000008</v>
+        <f>+AM7*1.3</f>
+        <v>13.520000000000001</v>
       </c>
       <c r="AO7" s="2">
-        <f>+AN7*1.05</f>
-        <v>337.7459085000001</v>
+        <f>+AN7*1.3</f>
+        <v>17.576000000000004</v>
       </c>
       <c r="AP7" s="2">
-        <f>+AO7*1.05</f>
-        <v>354.63320392500015</v>
+        <f>+AO7*1.1</f>
+        <v>19.333600000000008</v>
       </c>
       <c r="AQ7" s="2">
-        <f>+AP7*1.05</f>
-        <v>372.36486412125015</v>
+        <f>+AP7*1.1</f>
+        <v>21.266960000000012</v>
       </c>
       <c r="AR7" s="2">
-        <f>+AQ7*1.05</f>
-        <v>390.98310732731267</v>
-      </c>
-    </row>
-    <row r="8" spans="1:44" x14ac:dyDescent="0.25">
+        <f>+AQ7*1.1</f>
+        <v>23.393656000000014</v>
+      </c>
+      <c r="AS7" s="2">
+        <f>+AR7*1.05</f>
+        <v>24.563338800000015</v>
+      </c>
+      <c r="AT7" s="2">
+        <f>+AS7*1.05</f>
+        <v>25.791505740000016</v>
+      </c>
+      <c r="AU7" s="2">
+        <f>+AT7*1.05</f>
+        <v>27.081081027000018</v>
+      </c>
+      <c r="AV7" s="2">
+        <f>+AU7*1.05</f>
+        <v>28.435135078350019</v>
+      </c>
+    </row>
+    <row r="8" spans="1:48" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>73</v>
       </c>
@@ -2056,51 +2065,51 @@
       <c r="S8" s="1"/>
       <c r="T8" s="1"/>
       <c r="U8" s="1"/>
-      <c r="AH8" s="2">
+      <c r="AL8" s="2">
         <f>SUM(W8:Z8)</f>
         <v>0</v>
       </c>
-      <c r="AI8" s="2">
+      <c r="AM8" s="2">
         <v>1000</v>
       </c>
-      <c r="AJ8" s="2">
-        <f>+AI8*1.01</f>
+      <c r="AN8" s="2">
+        <f>+AM8*1.01</f>
         <v>1010</v>
       </c>
-      <c r="AK8" s="2">
-        <f t="shared" ref="AK8:AR8" si="2">+AJ8*1.01</f>
+      <c r="AO8" s="2">
+        <f t="shared" ref="AO8:AV8" si="2">+AN8*1.01</f>
         <v>1020.1</v>
       </c>
-      <c r="AL8" s="2">
+      <c r="AP8" s="2">
         <f t="shared" si="2"/>
         <v>1030.3009999999999</v>
       </c>
-      <c r="AM8" s="2">
+      <c r="AQ8" s="2">
         <f t="shared" si="2"/>
         <v>1040.60401</v>
       </c>
-      <c r="AN8" s="2">
+      <c r="AR8" s="2">
         <f t="shared" si="2"/>
         <v>1051.0100500999999</v>
       </c>
-      <c r="AO8" s="2">
+      <c r="AS8" s="2">
         <f t="shared" si="2"/>
         <v>1061.5201506009998</v>
       </c>
-      <c r="AP8" s="2">
+      <c r="AT8" s="2">
         <f t="shared" si="2"/>
         <v>1072.1353521070098</v>
       </c>
-      <c r="AQ8" s="2">
+      <c r="AU8" s="2">
         <f t="shared" si="2"/>
         <v>1082.8567056280799</v>
       </c>
-      <c r="AR8" s="2">
+      <c r="AV8" s="2">
         <f t="shared" si="2"/>
         <v>1093.6852726843608</v>
       </c>
     </row>
-    <row r="9" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:48" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>63</v>
       </c>
@@ -2111,52 +2120,52 @@
       <c r="S9" s="1"/>
       <c r="T9" s="1"/>
       <c r="U9" s="1"/>
-      <c r="AH9" s="2">
+      <c r="AL9" s="2">
         <f>SUM(W9:Z9)</f>
         <v>0</v>
       </c>
-      <c r="AI9" s="2">
-        <f t="shared" ref="AI9:AR9" si="3">+AH10*0.5</f>
-        <v>858.75</v>
-      </c>
-      <c r="AJ9" s="2">
-        <f t="shared" si="3"/>
-        <v>687</v>
-      </c>
-      <c r="AK9" s="2">
-        <f t="shared" si="3"/>
-        <v>549.6</v>
-      </c>
-      <c r="AL9" s="2">
-        <f t="shared" si="3"/>
-        <v>439.68000000000006</v>
-      </c>
       <c r="AM9" s="2">
-        <f t="shared" si="3"/>
-        <v>351.74400000000009</v>
+        <f t="shared" ref="AM9:AV9" si="3">+AL10*0.5</f>
+        <v>815.25</v>
       </c>
       <c r="AN9" s="2">
         <f t="shared" si="3"/>
-        <v>281.3952000000001</v>
+        <v>652.20000000000005</v>
       </c>
       <c r="AO9" s="2">
         <f t="shared" si="3"/>
-        <v>225.11616000000009</v>
+        <v>521.7600000000001</v>
       </c>
       <c r="AP9" s="2">
         <f t="shared" si="3"/>
-        <v>180.09292800000009</v>
+        <v>417.40800000000013</v>
       </c>
       <c r="AQ9" s="2">
         <f t="shared" si="3"/>
-        <v>144.07434240000006</v>
+        <v>333.92640000000011</v>
       </c>
       <c r="AR9" s="2">
         <f t="shared" si="3"/>
-        <v>115.25947392000006</v>
-      </c>
-    </row>
-    <row r="10" spans="1:44" x14ac:dyDescent="0.25">
+        <v>267.14112000000011</v>
+      </c>
+      <c r="AS9" s="2">
+        <f t="shared" si="3"/>
+        <v>213.71289600000011</v>
+      </c>
+      <c r="AT9" s="2">
+        <f t="shared" si="3"/>
+        <v>170.97031680000009</v>
+      </c>
+      <c r="AU9" s="2">
+        <f t="shared" si="3"/>
+        <v>136.77625344000009</v>
+      </c>
+      <c r="AV9" s="2">
+        <f t="shared" si="3"/>
+        <v>109.42100275200008</v>
+      </c>
+    </row>
+    <row r="10" spans="1:48" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>83</v>
       </c>
@@ -2184,71 +2193,74 @@
         <v>923</v>
       </c>
       <c r="W10" s="2">
-        <f>+S10</f>
-        <v>167</v>
+        <v>84</v>
       </c>
       <c r="X10" s="2">
-        <f>+T10</f>
-        <v>184</v>
+        <v>114</v>
       </c>
       <c r="Y10">
-        <f>+U10*0.5</f>
-        <v>905</v>
+        <v>971</v>
       </c>
       <c r="Z10" s="2">
         <f>+V10*0.5</f>
         <v>461.5</v>
       </c>
-      <c r="AG10" s="2">
+      <c r="AA10" s="2">
+        <v>345</v>
+      </c>
+      <c r="AB10" s="2"/>
+      <c r="AC10" s="2"/>
+      <c r="AD10" s="2"/>
+      <c r="AK10" s="2">
         <f>SUM(S10:V10)</f>
         <v>3084</v>
       </c>
-      <c r="AH10" s="2">
+      <c r="AL10" s="2">
         <f>SUM(W10:Z10)</f>
-        <v>1717.5</v>
-      </c>
-      <c r="AI10" s="2">
-        <f>+AH10*0.8</f>
-        <v>1374</v>
-      </c>
-      <c r="AJ10" s="2">
-        <f t="shared" ref="AJ10:AR10" si="4">+AI10*0.8</f>
-        <v>1099.2</v>
-      </c>
-      <c r="AK10" s="2">
-        <f t="shared" si="4"/>
-        <v>879.36000000000013</v>
-      </c>
-      <c r="AL10" s="2">
-        <f t="shared" si="4"/>
-        <v>703.48800000000017</v>
+        <v>1630.5</v>
       </c>
       <c r="AM10" s="2">
-        <f t="shared" si="4"/>
-        <v>562.7904000000002</v>
+        <f>+AL10*0.8</f>
+        <v>1304.4000000000001</v>
       </c>
       <c r="AN10" s="2">
-        <f t="shared" si="4"/>
-        <v>450.23232000000019</v>
+        <f t="shared" ref="AN10:AV10" si="4">+AM10*0.8</f>
+        <v>1043.5200000000002</v>
       </c>
       <c r="AO10" s="2">
         <f t="shared" si="4"/>
-        <v>360.18585600000017</v>
+        <v>834.81600000000026</v>
       </c>
       <c r="AP10" s="2">
         <f t="shared" si="4"/>
-        <v>288.14868480000013</v>
+        <v>667.85280000000023</v>
       </c>
       <c r="AQ10" s="2">
         <f t="shared" si="4"/>
-        <v>230.51894784000012</v>
+        <v>534.28224000000023</v>
       </c>
       <c r="AR10" s="2">
         <f t="shared" si="4"/>
-        <v>184.4151582720001</v>
-      </c>
-    </row>
-    <row r="11" spans="1:44" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>427.42579200000023</v>
+      </c>
+      <c r="AS10" s="2">
+        <f t="shared" si="4"/>
+        <v>341.94063360000018</v>
+      </c>
+      <c r="AT10" s="2">
+        <f t="shared" si="4"/>
+        <v>273.55250688000018</v>
+      </c>
+      <c r="AU10" s="2">
+        <f t="shared" si="4"/>
+        <v>218.84200550400016</v>
+      </c>
+      <c r="AV10" s="2">
+        <f t="shared" si="4"/>
+        <v>175.07360440320014</v>
+      </c>
+    </row>
+    <row r="11" spans="1:48" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B11" s="2" t="s">
         <v>8</v>
       </c>
@@ -2288,7 +2300,7 @@
         <v>1828</v>
       </c>
       <c r="P11" s="2">
-        <f t="shared" ref="P11:Z11" si="5">+P10+P7</f>
+        <f t="shared" ref="P11:AA11" si="5">+P10+P7</f>
         <v>293</v>
       </c>
       <c r="Q11" s="2">
@@ -2317,82 +2329,86 @@
       </c>
       <c r="W11" s="2">
         <f t="shared" si="5"/>
-        <v>187</v>
+        <v>86</v>
       </c>
       <c r="X11" s="2">
         <f t="shared" si="5"/>
-        <v>209</v>
+        <v>114</v>
       </c>
       <c r="Y11" s="2">
         <f t="shared" si="5"/>
-        <v>935</v>
+        <v>973</v>
       </c>
       <c r="Z11" s="2">
         <f t="shared" si="5"/>
-        <v>496.5</v>
-      </c>
-      <c r="AD11" s="2">
+        <v>465.5</v>
+      </c>
+      <c r="AA11" s="2">
+        <f t="shared" si="5"/>
+        <v>352</v>
+      </c>
+      <c r="AH11" s="2">
         <f>SUM(G11:J11)</f>
         <v>17675</v>
       </c>
-      <c r="AE11" s="2">
+      <c r="AI11" s="2">
         <f>SUM(K11:N11)</f>
         <v>18435</v>
       </c>
-      <c r="AF11" s="2">
+      <c r="AJ11" s="2">
         <f>SUM(O11:R11)</f>
         <v>6671</v>
       </c>
-      <c r="AG11" s="2">
-        <f>+AG10+AG7</f>
+      <c r="AK11" s="2">
+        <f>+AK10+AK7</f>
         <v>3134</v>
       </c>
-      <c r="AH11" s="2">
-        <f>SUM(AH7:AH10)</f>
-        <v>1827.5</v>
-      </c>
-      <c r="AI11" s="2">
-        <f t="shared" ref="AI11:AR11" si="6">+AH11*0.2</f>
-        <v>365.5</v>
-      </c>
-      <c r="AJ11" s="2">
-        <f t="shared" si="6"/>
-        <v>73.100000000000009</v>
-      </c>
-      <c r="AK11" s="2">
-        <f t="shared" si="6"/>
-        <v>14.620000000000003</v>
-      </c>
       <c r="AL11" s="2">
-        <f t="shared" si="6"/>
-        <v>2.9240000000000008</v>
+        <f>SUM(AL7:AL10)</f>
+        <v>1638.5</v>
       </c>
       <c r="AM11" s="2">
-        <f t="shared" si="6"/>
-        <v>0.58480000000000021</v>
+        <f t="shared" ref="AM11:AV11" si="6">+AL11*0.2</f>
+        <v>327.70000000000005</v>
       </c>
       <c r="AN11" s="2">
         <f t="shared" si="6"/>
-        <v>0.11696000000000005</v>
+        <v>65.540000000000006</v>
       </c>
       <c r="AO11" s="2">
         <f t="shared" si="6"/>
-        <v>2.339200000000001E-2</v>
+        <v>13.108000000000002</v>
       </c>
       <c r="AP11" s="2">
         <f t="shared" si="6"/>
-        <v>4.6784000000000018E-3</v>
+        <v>2.6216000000000008</v>
       </c>
       <c r="AQ11" s="2">
         <f t="shared" si="6"/>
-        <v>9.3568000000000037E-4</v>
+        <v>0.52432000000000023</v>
       </c>
       <c r="AR11" s="2">
         <f t="shared" si="6"/>
-        <v>1.8713600000000007E-4</v>
-      </c>
-    </row>
-    <row r="12" spans="1:44" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>0.10486400000000005</v>
+      </c>
+      <c r="AS11" s="2">
+        <f t="shared" si="6"/>
+        <v>2.0972800000000014E-2</v>
+      </c>
+      <c r="AT11" s="2">
+        <f t="shared" si="6"/>
+        <v>4.1945600000000026E-3</v>
+      </c>
+      <c r="AU11" s="2">
+        <f t="shared" si="6"/>
+        <v>8.3891200000000058E-4</v>
+      </c>
+      <c r="AV11" s="2">
+        <f t="shared" si="6"/>
+        <v>1.6778240000000014E-4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:48" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B12" s="2" t="s">
         <v>24</v>
       </c>
@@ -2426,38 +2442,26 @@
         <v>144</v>
       </c>
       <c r="N12" s="3"/>
-      <c r="AD12" s="2">
+      <c r="AH12" s="2">
         <f>SUM(G12:J12)</f>
         <v>735</v>
       </c>
-      <c r="AE12" s="2">
+      <c r="AI12" s="2">
         <f>SUM(K12:N12)</f>
         <v>453</v>
       </c>
-      <c r="AF12" s="2">
+      <c r="AJ12" s="2">
         <f>SUM(O12:R12)</f>
         <v>0</v>
       </c>
-      <c r="AG12" s="2">
+      <c r="AK12" s="2">
         <f>SUM(S12:V12)</f>
         <v>0</v>
       </c>
-      <c r="AH12" s="2">
+      <c r="AL12" s="2">
         <f>SUM(W12:Z12)</f>
         <v>0</v>
       </c>
-      <c r="AI12" s="2">
-        <v>0</v>
-      </c>
-      <c r="AJ12" s="2">
-        <v>0</v>
-      </c>
-      <c r="AK12" s="2">
-        <v>0</v>
-      </c>
-      <c r="AL12" s="2">
-        <v>0</v>
-      </c>
       <c r="AM12" s="2">
         <v>0</v>
       </c>
@@ -2476,8 +2480,20 @@
       <c r="AR12" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:44" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AS12" s="2">
+        <v>0</v>
+      </c>
+      <c r="AT12" s="2">
+        <v>0</v>
+      </c>
+      <c r="AU12" s="2">
+        <v>0</v>
+      </c>
+      <c r="AV12" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:48" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B13" s="2" t="s">
         <v>25</v>
       </c>
@@ -2538,83 +2554,83 @@
         <v>28</v>
       </c>
       <c r="W13" s="2">
-        <f>+S13</f>
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="X13" s="2">
-        <f>+T13</f>
-        <v>57</v>
+        <v>28</v>
       </c>
       <c r="Y13" s="2">
-        <f>+U13</f>
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Z13" s="2">
         <f>+V13</f>
         <v>28</v>
       </c>
-      <c r="AD13" s="2">
+      <c r="AA13" s="2">
+        <v>37</v>
+      </c>
+      <c r="AH13" s="2">
         <f>SUM(G13:J13)</f>
         <v>61</v>
       </c>
-      <c r="AE13" s="2">
+      <c r="AI13" s="2">
         <f>SUM(K13:N13)</f>
         <v>375</v>
       </c>
-      <c r="AF13" s="2">
+      <c r="AJ13" s="2">
         <f>SUM(O13:R13)</f>
         <v>177</v>
       </c>
-      <c r="AG13" s="2">
+      <c r="AK13" s="2">
         <f>SUM(S13:V13)</f>
         <v>127</v>
       </c>
-      <c r="AH13" s="2">
+      <c r="AL13" s="2">
         <f>SUM(W13:Z13)</f>
-        <v>127</v>
-      </c>
-      <c r="AI13" s="2">
-        <f>+AH13</f>
-        <v>127</v>
-      </c>
-      <c r="AJ13" s="2">
-        <f t="shared" ref="AJ13:AR13" si="7">+AI13</f>
-        <v>127</v>
-      </c>
-      <c r="AK13" s="2">
-        <f t="shared" si="7"/>
-        <v>127</v>
-      </c>
-      <c r="AL13" s="2">
-        <f t="shared" si="7"/>
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="AM13" s="2">
-        <f t="shared" si="7"/>
-        <v>127</v>
+        <f>+AL13</f>
+        <v>121</v>
       </c>
       <c r="AN13" s="2">
-        <f t="shared" si="7"/>
-        <v>127</v>
+        <f t="shared" ref="AN13:AV13" si="7">+AM13</f>
+        <v>121</v>
       </c>
       <c r="AO13" s="2">
         <f t="shared" si="7"/>
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="AP13" s="2">
         <f t="shared" si="7"/>
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="AQ13" s="2">
         <f t="shared" si="7"/>
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="AR13" s="2">
         <f t="shared" si="7"/>
-        <v>127</v>
-      </c>
-    </row>
-    <row r="14" spans="1:44" s="4" customFormat="1" ht="13" x14ac:dyDescent="0.3">
+        <v>121</v>
+      </c>
+      <c r="AS13" s="2">
+        <f t="shared" si="7"/>
+        <v>121</v>
+      </c>
+      <c r="AT13" s="2">
+        <f t="shared" si="7"/>
+        <v>121</v>
+      </c>
+      <c r="AU13" s="2">
+        <f t="shared" si="7"/>
+        <v>121</v>
+      </c>
+      <c r="AV13" s="2">
+        <f t="shared" si="7"/>
+        <v>121</v>
+      </c>
+    </row>
+    <row r="14" spans="1:48" s="4" customFormat="1" ht="13" x14ac:dyDescent="0.3">
       <c r="B14" s="4" t="s">
         <v>26</v>
       </c>
@@ -2673,7 +2689,7 @@
         <v>1831</v>
       </c>
       <c r="R14" s="5">
-        <f t="shared" ref="R14:Z14" si="13">SUM(R11:R13)</f>
+        <f t="shared" ref="R14:AD14" si="13">SUM(R11:R13)</f>
         <v>2811</v>
       </c>
       <c r="S14" s="5">
@@ -2694,82 +2710,98 @@
       </c>
       <c r="W14" s="5">
         <f t="shared" si="13"/>
-        <v>187</v>
+        <v>108</v>
       </c>
       <c r="X14" s="5">
         <f t="shared" si="13"/>
-        <v>266</v>
+        <v>142</v>
       </c>
       <c r="Y14" s="5">
         <f t="shared" si="13"/>
-        <v>977</v>
+        <v>1016</v>
       </c>
       <c r="Z14" s="5">
         <f t="shared" si="13"/>
-        <v>524.5</v>
-      </c>
-      <c r="AD14" s="4">
-        <f>SUM(AD11:AD13)</f>
+        <v>493.5</v>
+      </c>
+      <c r="AA14" s="5">
+        <f t="shared" si="13"/>
+        <v>389</v>
+      </c>
+      <c r="AB14" s="5">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="AC14" s="5">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="AD14" s="5">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="AH14" s="4">
+        <f>SUM(AH11:AH13)</f>
         <v>18471</v>
       </c>
-      <c r="AE14" s="4">
-        <f>SUM(AE11:AE13)</f>
+      <c r="AI14" s="4">
+        <f>SUM(AI11:AI13)</f>
         <v>19263</v>
       </c>
-      <c r="AF14" s="4">
-        <f>SUM(AF11:AF13)</f>
+      <c r="AJ14" s="4">
+        <f>SUM(AJ11:AJ13)</f>
         <v>6848</v>
       </c>
-      <c r="AG14" s="4">
-        <f>SUM(AG7:AG13)</f>
+      <c r="AK14" s="4">
+        <f>SUM(AK7:AK13)</f>
         <v>6395</v>
       </c>
-      <c r="AH14" s="4">
-        <f>+AH13+AH12+AH11</f>
-        <v>1954.5</v>
-      </c>
-      <c r="AI14" s="4">
-        <f>SUM(AI7:AI13)</f>
-        <v>3868.25</v>
-      </c>
-      <c r="AJ14" s="4">
-        <f>SUM(AJ7:AJ13)</f>
-        <v>3182.2000000000003</v>
-      </c>
-      <c r="AK14" s="4">
-        <f t="shared" ref="AK14:AR14" si="14">SUM(AK7:AK13)</f>
-        <v>2832.35</v>
-      </c>
       <c r="AL14" s="4">
-        <f t="shared" si="14"/>
-        <v>2569.23</v>
+        <f>+AL13+AL12+AL11</f>
+        <v>1759.5</v>
       </c>
       <c r="AM14" s="4">
-        <f t="shared" si="14"/>
-        <v>2375.1439100000007</v>
+        <f>SUM(AM7:AM13)</f>
+        <v>3578.75</v>
       </c>
       <c r="AN14" s="4">
-        <f t="shared" si="14"/>
-        <v>2231.4173001000004</v>
+        <f>SUM(AN7:AN13)</f>
+        <v>2905.78</v>
       </c>
       <c r="AO14" s="4">
-        <f t="shared" si="14"/>
-        <v>2111.591467101</v>
+        <f t="shared" ref="AO14:AV14" si="14">SUM(AO7:AO13)</f>
+        <v>2528.3600000000006</v>
       </c>
       <c r="AP14" s="4">
         <f t="shared" si="14"/>
-        <v>2022.0148472320102</v>
+        <v>2258.5170000000003</v>
       </c>
       <c r="AQ14" s="4">
         <f t="shared" si="14"/>
-        <v>1956.8157956693303</v>
+        <v>2051.6039300000002</v>
       </c>
       <c r="AR14" s="4">
         <f t="shared" si="14"/>
-        <v>1911.3431993396737</v>
-      </c>
-    </row>
-    <row r="15" spans="1:44" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>1890.0754821000003</v>
+      </c>
+      <c r="AS14" s="4">
+        <f t="shared" si="14"/>
+        <v>1762.7579918010001</v>
+      </c>
+      <c r="AT14" s="4">
+        <f t="shared" si="14"/>
+        <v>1663.4538760870103</v>
+      </c>
+      <c r="AU14" s="4">
+        <f t="shared" si="14"/>
+        <v>1586.5568845110802</v>
+      </c>
+      <c r="AV14" s="4">
+        <f t="shared" si="14"/>
+        <v>1527.6151827003109</v>
+      </c>
+    </row>
+    <row r="15" spans="1:48" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B15" s="2" t="s">
         <v>34</v>
       </c>
@@ -2829,52 +2861,64 @@
       <c r="V15" s="2">
         <v>739</v>
       </c>
-      <c r="AH15" s="2">
-        <f>+AH14-AH16</f>
-        <v>586.35000000000014</v>
-      </c>
-      <c r="AI15" s="2">
-        <f t="shared" ref="AI15:AR15" si="15">+AI14-AI16</f>
-        <v>1160.4750000000004</v>
-      </c>
-      <c r="AJ15" s="2">
-        <f t="shared" si="15"/>
-        <v>954.66000000000031</v>
-      </c>
-      <c r="AK15" s="2">
-        <f t="shared" si="15"/>
-        <v>849.70500000000015</v>
+      <c r="W15" s="2">
+        <v>90</v>
+      </c>
+      <c r="X15" s="2">
+        <v>28</v>
+      </c>
+      <c r="Y15" s="2">
+        <v>207</v>
+      </c>
+      <c r="AA15" s="2">
+        <v>955</v>
       </c>
       <c r="AL15" s="2">
-        <f t="shared" si="15"/>
-        <v>770.76900000000023</v>
+        <f>+AL14-AL16</f>
+        <v>527.85000000000014</v>
       </c>
       <c r="AM15" s="2">
-        <f t="shared" si="15"/>
-        <v>712.54317300000025</v>
+        <f t="shared" ref="AM15:AV15" si="15">+AM14-AM16</f>
+        <v>1073.625</v>
       </c>
       <c r="AN15" s="2">
         <f t="shared" si="15"/>
-        <v>669.42519003000029</v>
+        <v>871.73400000000015</v>
       </c>
       <c r="AO15" s="2">
         <f t="shared" si="15"/>
-        <v>633.47744013030001</v>
+        <v>758.50800000000027</v>
       </c>
       <c r="AP15" s="2">
         <f t="shared" si="15"/>
-        <v>606.60445416960306</v>
+        <v>677.55510000000027</v>
       </c>
       <c r="AQ15" s="2">
         <f t="shared" si="15"/>
-        <v>587.04473870079914</v>
+        <v>615.48117900000011</v>
       </c>
       <c r="AR15" s="2">
         <f t="shared" si="15"/>
-        <v>573.40295980190217</v>
-      </c>
-    </row>
-    <row r="16" spans="1:44" x14ac:dyDescent="0.25">
+        <v>567.02264463000006</v>
+      </c>
+      <c r="AS15" s="2">
+        <f t="shared" si="15"/>
+        <v>528.82739754030013</v>
+      </c>
+      <c r="AT15" s="2">
+        <f t="shared" si="15"/>
+        <v>499.03616282610324</v>
+      </c>
+      <c r="AU15" s="2">
+        <f t="shared" si="15"/>
+        <v>475.96706535332419</v>
+      </c>
+      <c r="AV15" s="2">
+        <f t="shared" si="15"/>
+        <v>458.28455481009337</v>
+      </c>
+    </row>
+    <row r="16" spans="1:48" x14ac:dyDescent="0.25">
       <c r="B16" s="2" t="s">
         <v>35</v>
       </c>
@@ -2950,52 +2994,68 @@
         <f>+V14-V15</f>
         <v>227</v>
       </c>
-      <c r="AH16" s="2">
-        <f>+AH14*0.7</f>
-        <v>1368.1499999999999</v>
-      </c>
-      <c r="AI16" s="2">
-        <f t="shared" ref="AI16:AR16" si="18">+AI14*0.7</f>
-        <v>2707.7749999999996</v>
-      </c>
-      <c r="AJ16" s="2">
-        <f t="shared" si="18"/>
-        <v>2227.54</v>
-      </c>
-      <c r="AK16" s="2">
-        <f t="shared" si="18"/>
-        <v>1982.6449999999998</v>
+      <c r="W16" s="2">
+        <f>+W14-W15</f>
+        <v>18</v>
+      </c>
+      <c r="X16" s="2">
+        <f t="shared" ref="X16" si="18">+X14-X15</f>
+        <v>114</v>
+      </c>
+      <c r="Y16" s="2">
+        <f>+Y14-Y15</f>
+        <v>809</v>
+      </c>
+      <c r="AA16" s="2">
+        <f>+AA14-AA15</f>
+        <v>-566</v>
       </c>
       <c r="AL16" s="2">
-        <f t="shared" si="18"/>
-        <v>1798.4609999999998</v>
+        <f>+AL14*0.7</f>
+        <v>1231.6499999999999</v>
       </c>
       <c r="AM16" s="2">
-        <f t="shared" si="18"/>
-        <v>1662.6007370000004</v>
+        <f t="shared" ref="AM16:AV16" si="19">+AM14*0.7</f>
+        <v>2505.125</v>
       </c>
       <c r="AN16" s="2">
-        <f t="shared" si="18"/>
-        <v>1561.9921100700001</v>
+        <f t="shared" si="19"/>
+        <v>2034.046</v>
       </c>
       <c r="AO16" s="2">
-        <f t="shared" si="18"/>
-        <v>1478.1140269707</v>
+        <f t="shared" si="19"/>
+        <v>1769.8520000000003</v>
       </c>
       <c r="AP16" s="2">
-        <f t="shared" si="18"/>
-        <v>1415.4103930624071</v>
+        <f t="shared" si="19"/>
+        <v>1580.9619</v>
       </c>
       <c r="AQ16" s="2">
-        <f t="shared" si="18"/>
-        <v>1369.7710569685312</v>
+        <f t="shared" si="19"/>
+        <v>1436.1227510000001</v>
       </c>
       <c r="AR16" s="2">
-        <f t="shared" si="18"/>
-        <v>1337.9402395377715</v>
-      </c>
-    </row>
-    <row r="17" spans="2:139" x14ac:dyDescent="0.25">
+        <f t="shared" si="19"/>
+        <v>1323.0528374700002</v>
+      </c>
+      <c r="AS16" s="2">
+        <f t="shared" si="19"/>
+        <v>1233.9305942607</v>
+      </c>
+      <c r="AT16" s="2">
+        <f t="shared" si="19"/>
+        <v>1164.417713260907</v>
+      </c>
+      <c r="AU16" s="2">
+        <f t="shared" si="19"/>
+        <v>1110.589819157756</v>
+      </c>
+      <c r="AV16" s="2">
+        <f t="shared" si="19"/>
+        <v>1069.3306278902176</v>
+      </c>
+    </row>
+    <row r="17" spans="2:143" x14ac:dyDescent="0.25">
       <c r="B17" s="2" t="s">
         <v>36</v>
       </c>
@@ -3053,8 +3113,17 @@
       <c r="V17" s="3">
         <v>1122</v>
       </c>
-    </row>
-    <row r="18" spans="2:139" x14ac:dyDescent="0.25">
+      <c r="W17" s="3">
+        <v>856</v>
+      </c>
+      <c r="X17" s="3">
+        <v>700</v>
+      </c>
+      <c r="Y17" s="3">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="18" spans="2:143" x14ac:dyDescent="0.25">
       <c r="B18" s="2" t="s">
         <v>37</v>
       </c>
@@ -3112,113 +3181,122 @@
       <c r="V18" s="2">
         <v>351</v>
       </c>
-      <c r="AH18" s="2">
-        <f>+AH14*0.25</f>
-        <v>488.625</v>
-      </c>
-      <c r="AI18" s="2">
-        <f t="shared" ref="AI18:AR18" si="19">+AI14*0.25</f>
-        <v>967.0625</v>
-      </c>
-      <c r="AJ18" s="2">
-        <f t="shared" si="19"/>
-        <v>795.55000000000007</v>
-      </c>
-      <c r="AK18" s="2">
-        <f t="shared" si="19"/>
-        <v>708.08749999999998</v>
+      <c r="W18" s="2">
+        <v>212</v>
+      </c>
+      <c r="X18" s="2">
+        <v>230</v>
+      </c>
+      <c r="Y18" s="2">
+        <v>268</v>
       </c>
       <c r="AL18" s="2">
-        <f t="shared" si="19"/>
-        <v>642.3075</v>
+        <f>+AL14*0.25</f>
+        <v>439.875</v>
       </c>
       <c r="AM18" s="2">
-        <f t="shared" si="19"/>
-        <v>593.78597750000017</v>
+        <f t="shared" ref="AM18:AV18" si="20">+AM14*0.25</f>
+        <v>894.6875</v>
       </c>
       <c r="AN18" s="2">
-        <f t="shared" si="19"/>
-        <v>557.85432502500009</v>
+        <f t="shared" si="20"/>
+        <v>726.44500000000005</v>
       </c>
       <c r="AO18" s="2">
-        <f t="shared" si="19"/>
-        <v>527.89786677525001</v>
+        <f t="shared" si="20"/>
+        <v>632.09000000000015</v>
       </c>
       <c r="AP18" s="2">
-        <f t="shared" si="19"/>
-        <v>505.50371180800255</v>
+        <f t="shared" si="20"/>
+        <v>564.62925000000007</v>
       </c>
       <c r="AQ18" s="2">
-        <f t="shared" si="19"/>
-        <v>489.20394891733258</v>
+        <f t="shared" si="20"/>
+        <v>512.90098250000005</v>
       </c>
       <c r="AR18" s="2">
-        <f t="shared" si="19"/>
-        <v>477.83579983491842</v>
-      </c>
-    </row>
-    <row r="19" spans="2:139" x14ac:dyDescent="0.25">
+        <f t="shared" si="20"/>
+        <v>472.51887052500007</v>
+      </c>
+      <c r="AS18" s="2">
+        <f t="shared" si="20"/>
+        <v>440.68949795025003</v>
+      </c>
+      <c r="AT18" s="2">
+        <f t="shared" si="20"/>
+        <v>415.86346902175256</v>
+      </c>
+      <c r="AU18" s="2">
+        <f t="shared" si="20"/>
+        <v>396.63922112777004</v>
+      </c>
+      <c r="AV18" s="2">
+        <f t="shared" si="20"/>
+        <v>381.90379567507773</v>
+      </c>
+    </row>
+    <row r="19" spans="2:143" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
         <v>32</v>
       </c>
       <c r="E19" s="1">
-        <f t="shared" ref="E19:L19" si="20">+E17+E18</f>
+        <f t="shared" ref="E19:L19" si="21">+E17+E18</f>
         <v>392</v>
       </c>
       <c r="F19" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>838</v>
       </c>
       <c r="G19" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>478</v>
       </c>
       <c r="H19" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>542</v>
       </c>
       <c r="I19" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>689</v>
       </c>
       <c r="J19" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>849</v>
       </c>
       <c r="K19" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>822</v>
       </c>
       <c r="L19" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>921</v>
       </c>
       <c r="M19" s="3">
-        <f t="shared" ref="M19:O19" si="21">+M17+M18</f>
+        <f t="shared" ref="M19:O19" si="22">+M17+M18</f>
         <v>1098</v>
       </c>
       <c r="N19" s="3">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>1586</v>
       </c>
       <c r="O19" s="3">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>1436</v>
       </c>
       <c r="P19" s="3">
-        <f t="shared" ref="P19" si="22">+P17+P18</f>
+        <f t="shared" ref="P19" si="23">+P17+P18</f>
         <v>1480</v>
       </c>
       <c r="Q19" s="3">
-        <f t="shared" ref="Q19" si="23">+Q17+Q18</f>
+        <f t="shared" ref="Q19" si="24">+Q17+Q18</f>
         <v>1602</v>
       </c>
       <c r="R19" s="3">
-        <f t="shared" ref="R19:S19" si="24">+R17+R18</f>
+        <f t="shared" ref="R19:S19" si="25">+R17+R18</f>
         <v>1876</v>
       </c>
       <c r="S19" s="3">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>1337</v>
       </c>
       <c r="T19" s="3">
@@ -3233,114 +3311,146 @@
         <f>+V18+V17</f>
         <v>1473</v>
       </c>
-      <c r="AH19" s="2">
-        <f>+AH18+AH17</f>
-        <v>488.625</v>
-      </c>
-      <c r="AI19" s="2">
-        <f t="shared" ref="AI19:AR19" si="25">+AI18+AI17</f>
-        <v>967.0625</v>
-      </c>
-      <c r="AJ19" s="2">
-        <f t="shared" si="25"/>
-        <v>795.55000000000007</v>
-      </c>
-      <c r="AK19" s="2">
-        <f t="shared" si="25"/>
-        <v>708.08749999999998</v>
+      <c r="W19" s="3">
+        <f t="shared" ref="W19:AD19" si="26">+W18+W17</f>
+        <v>1068</v>
+      </c>
+      <c r="X19" s="3">
+        <f t="shared" si="26"/>
+        <v>930</v>
+      </c>
+      <c r="Y19" s="3">
+        <f t="shared" si="26"/>
+        <v>1069</v>
+      </c>
+      <c r="Z19" s="3">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="AA19" s="3">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="AB19" s="3">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="AC19" s="3">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="AD19" s="3">
+        <f t="shared" si="26"/>
+        <v>0</v>
       </c>
       <c r="AL19" s="2">
-        <f t="shared" si="25"/>
-        <v>642.3075</v>
+        <f>+AL18+AL17</f>
+        <v>439.875</v>
       </c>
       <c r="AM19" s="2">
-        <f t="shared" si="25"/>
-        <v>593.78597750000017</v>
+        <f t="shared" ref="AM19:AV19" si="27">+AM18+AM17</f>
+        <v>894.6875</v>
       </c>
       <c r="AN19" s="2">
-        <f t="shared" si="25"/>
-        <v>557.85432502500009</v>
+        <f t="shared" si="27"/>
+        <v>726.44500000000005</v>
       </c>
       <c r="AO19" s="2">
-        <f t="shared" si="25"/>
-        <v>527.89786677525001</v>
+        <f t="shared" si="27"/>
+        <v>632.09000000000015</v>
       </c>
       <c r="AP19" s="2">
-        <f t="shared" si="25"/>
-        <v>505.50371180800255</v>
+        <f t="shared" si="27"/>
+        <v>564.62925000000007</v>
       </c>
       <c r="AQ19" s="2">
-        <f t="shared" si="25"/>
-        <v>489.20394891733258</v>
+        <f t="shared" si="27"/>
+        <v>512.90098250000005</v>
       </c>
       <c r="AR19" s="2">
-        <f t="shared" si="25"/>
-        <v>477.83579983491842</v>
-      </c>
-      <c r="AS19" s="2"/>
-    </row>
-    <row r="20" spans="2:139" x14ac:dyDescent="0.25">
+        <f t="shared" si="27"/>
+        <v>472.51887052500007</v>
+      </c>
+      <c r="AS19" s="2">
+        <f t="shared" si="27"/>
+        <v>440.68949795025003</v>
+      </c>
+      <c r="AT19" s="2">
+        <f t="shared" si="27"/>
+        <v>415.86346902175256</v>
+      </c>
+      <c r="AU19" s="2">
+        <f t="shared" si="27"/>
+        <v>396.63922112777004</v>
+      </c>
+      <c r="AV19" s="2">
+        <f t="shared" si="27"/>
+        <v>381.90379567507773</v>
+      </c>
+      <c r="AW19" s="2"/>
+    </row>
+    <row r="20" spans="2:143" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
         <v>33</v>
       </c>
       <c r="E20" s="3">
-        <f t="shared" ref="E20:L20" si="26">+E16-E19</f>
+        <f t="shared" ref="E20:L20" si="28">+E16-E19</f>
         <v>-235</v>
       </c>
       <c r="F20" s="3">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>-275</v>
       </c>
       <c r="G20" s="3">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>1266</v>
       </c>
       <c r="H20" s="3">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>3062</v>
       </c>
       <c r="I20" s="3">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>3558</v>
       </c>
       <c r="J20" s="3">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>5410</v>
       </c>
       <c r="K20" s="3">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>4227</v>
       </c>
       <c r="L20" s="3">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>2447</v>
       </c>
       <c r="M20" s="3">
-        <f t="shared" ref="M20:O20" si="27">+M16-M19</f>
+        <f t="shared" ref="M20:O20" si="29">+M16-M19</f>
         <v>1166</v>
       </c>
       <c r="N20" s="3">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>1580</v>
       </c>
       <c r="O20" s="3">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>-366</v>
       </c>
       <c r="P20" s="3">
-        <f t="shared" ref="P20" si="28">+P16-P19</f>
+        <f t="shared" ref="P20" si="30">+P16-P19</f>
         <v>-1867</v>
       </c>
       <c r="Q20" s="3">
-        <f t="shared" ref="Q20" si="29">+Q16-Q19</f>
+        <f t="shared" ref="Q20" si="31">+Q16-Q19</f>
         <v>-2012</v>
       </c>
       <c r="R20" s="3">
-        <f t="shared" ref="R20:S20" si="30">+R16-R19</f>
+        <f t="shared" ref="R20:S20" si="32">+R16-R19</f>
         <v>6</v>
       </c>
       <c r="S20" s="3">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>-1266</v>
       </c>
       <c r="T20" s="3">
@@ -3355,53 +3465,85 @@
         <f>+V16-V19</f>
         <v>-1246</v>
       </c>
-      <c r="AH20" s="2">
-        <f>+AH16-AH19</f>
-        <v>879.52499999999986</v>
-      </c>
-      <c r="AI20" s="2">
-        <f t="shared" ref="AI20:AR20" si="31">+AI16-AI19</f>
-        <v>1740.7124999999996</v>
-      </c>
-      <c r="AJ20" s="2">
-        <f t="shared" si="31"/>
-        <v>1431.9899999999998</v>
-      </c>
-      <c r="AK20" s="2">
-        <f t="shared" si="31"/>
-        <v>1274.5574999999999</v>
+      <c r="W20" s="3">
+        <f t="shared" ref="W20:AD20" si="33">+W16-W19</f>
+        <v>-1050</v>
+      </c>
+      <c r="X20" s="3">
+        <f t="shared" si="33"/>
+        <v>-816</v>
+      </c>
+      <c r="Y20" s="3">
+        <f t="shared" si="33"/>
+        <v>-260</v>
+      </c>
+      <c r="Z20" s="3">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="AA20" s="3">
+        <f t="shared" si="33"/>
+        <v>-566</v>
+      </c>
+      <c r="AB20" s="3">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="AC20" s="3">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="AD20" s="3">
+        <f t="shared" si="33"/>
+        <v>0</v>
       </c>
       <c r="AL20" s="2">
-        <f t="shared" si="31"/>
-        <v>1156.1534999999999</v>
+        <f>+AL16-AL19</f>
+        <v>791.77499999999986</v>
       </c>
       <c r="AM20" s="2">
-        <f t="shared" si="31"/>
-        <v>1068.8147595000003</v>
+        <f t="shared" ref="AM20:AV20" si="34">+AM16-AM19</f>
+        <v>1610.4375</v>
       </c>
       <c r="AN20" s="2">
-        <f t="shared" si="31"/>
-        <v>1004.137785045</v>
+        <f t="shared" si="34"/>
+        <v>1307.6010000000001</v>
       </c>
       <c r="AO20" s="2">
-        <f t="shared" si="31"/>
-        <v>950.21616019545002</v>
+        <f t="shared" si="34"/>
+        <v>1137.7620000000002</v>
       </c>
       <c r="AP20" s="2">
-        <f t="shared" si="31"/>
-        <v>909.90668125440459</v>
+        <f t="shared" si="34"/>
+        <v>1016.3326499999999</v>
       </c>
       <c r="AQ20" s="2">
-        <f t="shared" si="31"/>
-        <v>880.5671080511986</v>
+        <f t="shared" si="34"/>
+        <v>923.22176850000005</v>
       </c>
       <c r="AR20" s="2">
-        <f t="shared" si="31"/>
-        <v>860.10443970285314</v>
-      </c>
-      <c r="AS20" s="2"/>
-    </row>
-    <row r="21" spans="2:139" x14ac:dyDescent="0.25">
+        <f t="shared" si="34"/>
+        <v>850.5339669450002</v>
+      </c>
+      <c r="AS20" s="2">
+        <f t="shared" si="34"/>
+        <v>793.24109631044996</v>
+      </c>
+      <c r="AT20" s="2">
+        <f t="shared" si="34"/>
+        <v>748.55424423915451</v>
+      </c>
+      <c r="AU20" s="2">
+        <f t="shared" si="34"/>
+        <v>713.95059802998594</v>
+      </c>
+      <c r="AV20" s="2">
+        <f t="shared" si="34"/>
+        <v>687.42683221513983</v>
+      </c>
+      <c r="AW20" s="2"/>
+    </row>
+    <row r="21" spans="2:143" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
         <v>31</v>
       </c>
@@ -3476,69 +3618,78 @@
         <f>91-29</f>
         <v>62</v>
       </c>
-    </row>
-    <row r="22" spans="2:139" x14ac:dyDescent="0.25">
+      <c r="W21">
+        <v>90</v>
+      </c>
+      <c r="X21">
+        <v>81</v>
+      </c>
+      <c r="Y21">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="22" spans="2:143" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
         <v>30</v>
       </c>
       <c r="E22" s="3">
-        <f t="shared" ref="E22:L22" si="32">+E20+E21</f>
+        <f t="shared" ref="E22:L22" si="35">+E20+E21</f>
         <v>-232</v>
       </c>
       <c r="F22" s="3">
-        <f t="shared" si="32"/>
+        <f t="shared" si="35"/>
         <v>-271</v>
       </c>
       <c r="G22" s="3">
-        <f t="shared" si="32"/>
+        <f t="shared" si="35"/>
         <v>1260</v>
       </c>
       <c r="H22" s="3">
-        <f t="shared" si="32"/>
+        <f t="shared" si="35"/>
         <v>3063</v>
       </c>
       <c r="I22" s="3">
-        <f t="shared" si="32"/>
+        <f t="shared" si="35"/>
         <v>3552</v>
       </c>
       <c r="J22" s="3">
-        <f t="shared" si="32"/>
+        <f t="shared" si="35"/>
         <v>5410</v>
       </c>
       <c r="K22" s="3">
-        <f t="shared" si="32"/>
+        <f t="shared" si="35"/>
         <v>4229</v>
       </c>
       <c r="L22" s="3">
-        <f t="shared" si="32"/>
+        <f t="shared" si="35"/>
         <v>2474</v>
       </c>
       <c r="M22" s="3">
-        <f t="shared" ref="M22:S22" si="33">+M20+M21</f>
+        <f t="shared" ref="M22:S22" si="36">+M20+M21</f>
         <v>1217</v>
       </c>
       <c r="N22" s="3">
-        <f t="shared" si="33"/>
+        <f t="shared" si="36"/>
         <v>1655</v>
       </c>
       <c r="O22" s="3">
-        <f t="shared" si="33"/>
+        <f t="shared" si="36"/>
         <v>-305</v>
       </c>
       <c r="P22" s="3">
-        <f t="shared" si="33"/>
+        <f t="shared" si="36"/>
         <v>-1749</v>
       </c>
       <c r="Q22" s="3">
-        <f t="shared" si="33"/>
+        <f t="shared" si="36"/>
         <v>-1958</v>
       </c>
       <c r="R22" s="3">
-        <f t="shared" si="33"/>
+        <f t="shared" si="36"/>
         <v>70</v>
       </c>
       <c r="S22" s="3">
-        <f t="shared" si="33"/>
+        <f t="shared" si="36"/>
         <v>-1165</v>
       </c>
       <c r="T22" s="3">
@@ -3553,52 +3704,84 @@
         <f>+V20+V21</f>
         <v>-1184</v>
       </c>
-      <c r="AH22" s="2">
-        <f>+AH20+AH21</f>
-        <v>879.52499999999986</v>
-      </c>
-      <c r="AI22" s="2">
-        <f t="shared" ref="AI22:AR22" si="34">+AI20+AI21</f>
-        <v>1740.7124999999996</v>
-      </c>
-      <c r="AJ22" s="2">
-        <f t="shared" si="34"/>
-        <v>1431.9899999999998</v>
-      </c>
-      <c r="AK22" s="2">
-        <f t="shared" si="34"/>
-        <v>1274.5574999999999</v>
+      <c r="W22" s="3">
+        <f t="shared" ref="W22:AD22" si="37">+W20+W21</f>
+        <v>-960</v>
+      </c>
+      <c r="X22" s="3">
+        <f t="shared" si="37"/>
+        <v>-735</v>
+      </c>
+      <c r="Y22" s="3">
+        <f t="shared" si="37"/>
+        <v>-187</v>
+      </c>
+      <c r="Z22" s="3">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="AA22" s="3">
+        <f t="shared" si="37"/>
+        <v>-566</v>
+      </c>
+      <c r="AB22" s="3">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="AC22" s="3">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="AD22" s="3">
+        <f t="shared" si="37"/>
+        <v>0</v>
       </c>
       <c r="AL22" s="2">
-        <f t="shared" si="34"/>
-        <v>1156.1534999999999</v>
+        <f>+AL20+AL21</f>
+        <v>791.77499999999986</v>
       </c>
       <c r="AM22" s="2">
-        <f t="shared" si="34"/>
-        <v>1068.8147595000003</v>
+        <f t="shared" ref="AM22:AV22" si="38">+AM20+AM21</f>
+        <v>1610.4375</v>
       </c>
       <c r="AN22" s="2">
-        <f t="shared" si="34"/>
-        <v>1004.137785045</v>
+        <f t="shared" si="38"/>
+        <v>1307.6010000000001</v>
       </c>
       <c r="AO22" s="2">
-        <f t="shared" si="34"/>
-        <v>950.21616019545002</v>
+        <f t="shared" si="38"/>
+        <v>1137.7620000000002</v>
       </c>
       <c r="AP22" s="2">
-        <f t="shared" si="34"/>
-        <v>909.90668125440459</v>
+        <f t="shared" si="38"/>
+        <v>1016.3326499999999</v>
       </c>
       <c r="AQ22" s="2">
-        <f t="shared" si="34"/>
-        <v>880.5671080511986</v>
+        <f t="shared" si="38"/>
+        <v>923.22176850000005</v>
       </c>
       <c r="AR22" s="2">
-        <f t="shared" si="34"/>
-        <v>860.10443970285314</v>
-      </c>
-    </row>
-    <row r="23" spans="2:139" x14ac:dyDescent="0.25">
+        <f t="shared" si="38"/>
+        <v>850.5339669450002</v>
+      </c>
+      <c r="AS22" s="2">
+        <f t="shared" si="38"/>
+        <v>793.24109631044996</v>
+      </c>
+      <c r="AT22" s="2">
+        <f t="shared" si="38"/>
+        <v>748.55424423915451</v>
+      </c>
+      <c r="AU22" s="2">
+        <f t="shared" si="38"/>
+        <v>713.95059802998594</v>
+      </c>
+      <c r="AV22" s="2">
+        <f t="shared" si="38"/>
+        <v>687.42683221513983</v>
+      </c>
+    </row>
+    <row r="23" spans="2:143" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
         <v>29</v>
       </c>
@@ -3656,113 +3839,122 @@
       <c r="V23" s="3">
         <v>-64</v>
       </c>
-      <c r="AH23" s="2">
-        <f>+AH22*0.2</f>
-        <v>175.90499999999997</v>
-      </c>
-      <c r="AI23" s="2">
-        <f t="shared" ref="AI23:AR23" si="35">+AI22*0.2</f>
-        <v>348.14249999999993</v>
-      </c>
-      <c r="AJ23" s="2">
-        <f t="shared" si="35"/>
-        <v>286.39799999999997</v>
-      </c>
-      <c r="AK23" s="2">
-        <f t="shared" si="35"/>
-        <v>254.91149999999999</v>
+      <c r="W23" s="3">
+        <v>7</v>
+      </c>
+      <c r="X23" s="3">
+        <v>7</v>
+      </c>
+      <c r="Y23" s="3">
+        <v>13</v>
       </c>
       <c r="AL23" s="2">
-        <f t="shared" si="35"/>
-        <v>231.23069999999998</v>
+        <f>+AL22*0.2</f>
+        <v>158.35499999999999</v>
       </c>
       <c r="AM23" s="2">
-        <f t="shared" si="35"/>
-        <v>213.76295190000008</v>
+        <f t="shared" ref="AM23:AV23" si="39">+AM22*0.2</f>
+        <v>322.08750000000003</v>
       </c>
       <c r="AN23" s="2">
-        <f t="shared" si="35"/>
-        <v>200.827557009</v>
+        <f t="shared" si="39"/>
+        <v>261.52020000000005</v>
       </c>
       <c r="AO23" s="2">
-        <f t="shared" si="35"/>
-        <v>190.04323203909001</v>
+        <f t="shared" si="39"/>
+        <v>227.55240000000003</v>
       </c>
       <c r="AP23" s="2">
-        <f t="shared" si="35"/>
-        <v>181.98133625088093</v>
+        <f t="shared" si="39"/>
+        <v>203.26652999999999</v>
       </c>
       <c r="AQ23" s="2">
-        <f t="shared" si="35"/>
-        <v>176.11342161023973</v>
+        <f t="shared" si="39"/>
+        <v>184.64435370000001</v>
       </c>
       <c r="AR23" s="2">
-        <f t="shared" si="35"/>
-        <v>172.02088794057065</v>
-      </c>
-    </row>
-    <row r="24" spans="2:139" x14ac:dyDescent="0.25">
+        <f t="shared" si="39"/>
+        <v>170.10679338900005</v>
+      </c>
+      <c r="AS23" s="2">
+        <f t="shared" si="39"/>
+        <v>158.64821926209001</v>
+      </c>
+      <c r="AT23" s="2">
+        <f t="shared" si="39"/>
+        <v>149.7108488478309</v>
+      </c>
+      <c r="AU23" s="2">
+        <f t="shared" si="39"/>
+        <v>142.79011960599721</v>
+      </c>
+      <c r="AV23" s="2">
+        <f t="shared" si="39"/>
+        <v>137.48536644302797</v>
+      </c>
+    </row>
+    <row r="24" spans="2:143" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
         <v>28</v>
       </c>
       <c r="E24" s="3">
-        <f t="shared" ref="E24:L24" si="36">+E22-E23</f>
+        <f t="shared" ref="E24:L24" si="40">+E22-E23</f>
         <v>-233</v>
       </c>
       <c r="F24" s="3">
-        <f t="shared" si="36"/>
+        <f t="shared" si="40"/>
         <v>-272</v>
       </c>
       <c r="G24" s="3">
-        <f t="shared" si="36"/>
+        <f t="shared" si="40"/>
         <v>1221</v>
       </c>
       <c r="H24" s="3">
-        <f t="shared" si="36"/>
+        <f t="shared" si="40"/>
         <v>2780</v>
       </c>
       <c r="I24" s="3">
-        <f t="shared" si="36"/>
+        <f t="shared" si="40"/>
         <v>3333</v>
       </c>
       <c r="J24" s="3">
-        <f t="shared" si="36"/>
+        <f t="shared" si="40"/>
         <v>4868</v>
       </c>
       <c r="K24" s="3">
-        <f t="shared" si="36"/>
+        <f t="shared" si="40"/>
         <v>3657</v>
       </c>
       <c r="L24" s="3">
-        <f t="shared" si="36"/>
+        <f t="shared" si="40"/>
         <v>2197</v>
       </c>
       <c r="M24" s="3">
-        <f t="shared" ref="M24:S24" si="37">+M22-M23</f>
+        <f t="shared" ref="M24:S24" si="41">+M22-M23</f>
         <v>1043</v>
       </c>
       <c r="N24" s="3">
-        <f t="shared" si="37"/>
+        <f t="shared" si="41"/>
         <v>1465</v>
       </c>
       <c r="O24" s="3">
-        <f t="shared" si="37"/>
+        <f t="shared" si="41"/>
         <v>79</v>
       </c>
       <c r="P24" s="3">
-        <f t="shared" si="37"/>
+        <f t="shared" si="41"/>
         <v>-1380</v>
       </c>
       <c r="Q24" s="3">
-        <f t="shared" si="37"/>
+        <f t="shared" si="41"/>
         <v>-3630</v>
       </c>
       <c r="R24" s="3">
-        <f t="shared" si="37"/>
+        <f t="shared" si="41"/>
         <v>217</v>
       </c>
       <c r="S24" s="3">
-        <f t="shared" si="37"/>
+        <f t="shared" si="41"/>
         <v>-1175</v>
       </c>
       <c r="T24" s="3">
@@ -3777,493 +3969,525 @@
         <f>+V22-V23</f>
         <v>-1120</v>
       </c>
-      <c r="AH24" s="2">
-        <f>+AH22-AH23</f>
-        <v>703.61999999999989</v>
-      </c>
-      <c r="AI24" s="2">
-        <f t="shared" ref="AI24:AR24" si="38">+AI22-AI23</f>
-        <v>1392.5699999999997</v>
-      </c>
-      <c r="AJ24" s="2">
-        <f t="shared" si="38"/>
-        <v>1145.5919999999999</v>
-      </c>
-      <c r="AK24" s="2">
-        <f t="shared" si="38"/>
-        <v>1019.646</v>
+      <c r="W24" s="3">
+        <f t="shared" ref="W24:AD24" si="42">+W22-W23</f>
+        <v>-967</v>
+      </c>
+      <c r="X24" s="3">
+        <f t="shared" si="42"/>
+        <v>-742</v>
+      </c>
+      <c r="Y24" s="3">
+        <f t="shared" si="42"/>
+        <v>-200</v>
+      </c>
+      <c r="Z24" s="3">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="AA24" s="3">
+        <f t="shared" si="42"/>
+        <v>-566</v>
+      </c>
+      <c r="AB24" s="3">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="AC24" s="3">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="AD24" s="3">
+        <f t="shared" si="42"/>
+        <v>0</v>
       </c>
       <c r="AL24" s="2">
-        <f t="shared" si="38"/>
-        <v>924.92279999999994</v>
+        <f>+AL22-AL23</f>
+        <v>633.41999999999985</v>
       </c>
       <c r="AM24" s="2">
-        <f t="shared" si="38"/>
-        <v>855.05180760000019</v>
+        <f t="shared" ref="AM24:AV24" si="43">+AM22-AM23</f>
+        <v>1288.3499999999999</v>
       </c>
       <c r="AN24" s="2">
-        <f t="shared" si="38"/>
-        <v>803.31022803600001</v>
+        <f t="shared" si="43"/>
+        <v>1046.0808000000002</v>
       </c>
       <c r="AO24" s="2">
-        <f t="shared" si="38"/>
-        <v>760.17292815636006</v>
+        <f t="shared" si="43"/>
+        <v>910.20960000000014</v>
       </c>
       <c r="AP24" s="2">
-        <f t="shared" si="38"/>
-        <v>727.92534500352372</v>
+        <f t="shared" si="43"/>
+        <v>813.06611999999996</v>
       </c>
       <c r="AQ24" s="2">
-        <f t="shared" si="38"/>
-        <v>704.4536864409589</v>
+        <f t="shared" si="43"/>
+        <v>738.57741480000004</v>
       </c>
       <c r="AR24" s="2">
-        <f t="shared" si="38"/>
-        <v>688.08355176228247</v>
+        <f t="shared" si="43"/>
+        <v>680.42717355600018</v>
       </c>
       <c r="AS24" s="2">
-        <f>+AR24*(1+$AU$30)</f>
-        <v>653.67937417416829</v>
+        <f t="shared" si="43"/>
+        <v>634.59287704835992</v>
       </c>
       <c r="AT24" s="2">
-        <f t="shared" ref="AT24:DE24" si="39">+AS24*(1+$AU$30)</f>
-        <v>620.99540546545984</v>
+        <f t="shared" si="43"/>
+        <v>598.84339539132361</v>
       </c>
       <c r="AU24" s="2">
-        <f t="shared" si="39"/>
-        <v>589.94563519218684</v>
+        <f t="shared" si="43"/>
+        <v>571.16047842398871</v>
       </c>
       <c r="AV24" s="2">
-        <f t="shared" si="39"/>
-        <v>560.44835343257751</v>
+        <f t="shared" si="43"/>
+        <v>549.94146577211188</v>
       </c>
       <c r="AW24" s="2">
-        <f t="shared" si="39"/>
-        <v>532.42593576094862</v>
+        <f>+AV24*(1+$AY$30)</f>
+        <v>522.44439248350625</v>
       </c>
       <c r="AX24" s="2">
-        <f t="shared" si="39"/>
-        <v>505.80463897290116</v>
+        <f t="shared" ref="AX24:DI24" si="44">+AW24*(1+$AY$30)</f>
+        <v>496.32217285933092</v>
       </c>
       <c r="AY24" s="2">
-        <f t="shared" si="39"/>
-        <v>480.51440702425606</v>
+        <f t="shared" si="44"/>
+        <v>471.50606421636434</v>
       </c>
       <c r="AZ24" s="2">
-        <f t="shared" si="39"/>
-        <v>456.48868667304322</v>
+        <f t="shared" si="44"/>
+        <v>447.93076100554612</v>
       </c>
       <c r="BA24" s="2">
-        <f t="shared" si="39"/>
-        <v>433.66425233939106</v>
+        <f t="shared" si="44"/>
+        <v>425.53422295526877</v>
       </c>
       <c r="BB24" s="2">
-        <f t="shared" si="39"/>
-        <v>411.98103972242149</v>
+        <f t="shared" si="44"/>
+        <v>404.2575118075053</v>
       </c>
       <c r="BC24" s="2">
-        <f t="shared" si="39"/>
-        <v>391.3819877363004</v>
+        <f t="shared" si="44"/>
+        <v>384.04463621713001</v>
       </c>
       <c r="BD24" s="2">
-        <f t="shared" si="39"/>
-        <v>371.81288834948538</v>
+        <f t="shared" si="44"/>
+        <v>364.84240440627349</v>
       </c>
       <c r="BE24" s="2">
-        <f t="shared" si="39"/>
-        <v>353.22224393201111</v>
+        <f t="shared" si="44"/>
+        <v>346.60028418595982</v>
       </c>
       <c r="BF24" s="2">
-        <f t="shared" si="39"/>
-        <v>335.56113173541053</v>
+        <f t="shared" si="44"/>
+        <v>329.27026997666184</v>
       </c>
       <c r="BG24" s="2">
-        <f t="shared" si="39"/>
-        <v>318.78307514863997</v>
+        <f t="shared" si="44"/>
+        <v>312.80675647782874</v>
       </c>
       <c r="BH24" s="2">
-        <f t="shared" si="39"/>
-        <v>302.84392139120797</v>
+        <f t="shared" si="44"/>
+        <v>297.16641865393728</v>
       </c>
       <c r="BI24" s="2">
-        <f t="shared" si="39"/>
-        <v>287.70172532164759</v>
+        <f t="shared" si="44"/>
+        <v>282.30809772124042</v>
       </c>
       <c r="BJ24" s="2">
-        <f t="shared" si="39"/>
-        <v>273.31663905556519</v>
+        <f t="shared" si="44"/>
+        <v>268.19269283517838</v>
       </c>
       <c r="BK24" s="2">
-        <f t="shared" si="39"/>
-        <v>259.65080710278693</v>
+        <f t="shared" si="44"/>
+        <v>254.78305819341944</v>
       </c>
       <c r="BL24" s="2">
-        <f t="shared" si="39"/>
-        <v>246.66826674764758</v>
+        <f t="shared" si="44"/>
+        <v>242.04390528374844</v>
       </c>
       <c r="BM24" s="2">
-        <f t="shared" si="39"/>
-        <v>234.3348534102652</v>
+        <f t="shared" si="44"/>
+        <v>229.94171001956101</v>
       </c>
       <c r="BN24" s="2">
-        <f t="shared" si="39"/>
-        <v>222.61811073975193</v>
+        <f t="shared" si="44"/>
+        <v>218.44462451858294</v>
       </c>
       <c r="BO24" s="2">
-        <f t="shared" si="39"/>
-        <v>211.48720520276433</v>
+        <f t="shared" si="44"/>
+        <v>207.52239329265379</v>
       </c>
       <c r="BP24" s="2">
-        <f t="shared" si="39"/>
-        <v>200.91284494262609</v>
+        <f t="shared" si="44"/>
+        <v>197.14627362802108</v>
       </c>
       <c r="BQ24" s="2">
-        <f t="shared" si="39"/>
-        <v>190.86720269549477</v>
+        <f t="shared" si="44"/>
+        <v>187.28895994662003</v>
       </c>
       <c r="BR24" s="2">
-        <f t="shared" si="39"/>
-        <v>181.32384256072001</v>
+        <f t="shared" si="44"/>
+        <v>177.92451194928901</v>
       </c>
       <c r="BS24" s="2">
-        <f t="shared" si="39"/>
-        <v>172.25765043268399</v>
+        <f t="shared" si="44"/>
+        <v>169.02828635182456</v>
       </c>
       <c r="BT24" s="2">
-        <f t="shared" si="39"/>
-        <v>163.64476791104977</v>
+        <f t="shared" si="44"/>
+        <v>160.57687203423333</v>
       </c>
       <c r="BU24" s="2">
-        <f t="shared" si="39"/>
-        <v>155.46252951549727</v>
+        <f t="shared" si="44"/>
+        <v>152.54802843252165</v>
       </c>
       <c r="BV24" s="2">
-        <f t="shared" si="39"/>
-        <v>147.68940303972241</v>
+        <f t="shared" si="44"/>
+        <v>144.92062701089557</v>
       </c>
       <c r="BW24" s="2">
-        <f t="shared" si="39"/>
-        <v>140.30493288773627</v>
+        <f t="shared" si="44"/>
+        <v>137.67459566035078</v>
       </c>
       <c r="BX24" s="2">
-        <f t="shared" si="39"/>
-        <v>133.28968624334945</v>
+        <f t="shared" si="44"/>
+        <v>130.79086587733323</v>
       </c>
       <c r="BY24" s="2">
-        <f t="shared" si="39"/>
-        <v>126.62520193118198</v>
+        <f t="shared" si="44"/>
+        <v>124.25132258346656</v>
       </c>
       <c r="BZ24" s="2">
-        <f t="shared" si="39"/>
-        <v>120.29394183462287</v>
+        <f t="shared" si="44"/>
+        <v>118.03875645429322</v>
       </c>
       <c r="CA24" s="2">
-        <f t="shared" si="39"/>
-        <v>114.27924474289172</v>
+        <f t="shared" si="44"/>
+        <v>112.13681863157855</v>
       </c>
       <c r="CB24" s="2">
-        <f t="shared" si="39"/>
-        <v>108.56528250574713</v>
+        <f t="shared" si="44"/>
+        <v>106.52997769999962</v>
       </c>
       <c r="CC24" s="2">
-        <f t="shared" si="39"/>
-        <v>103.13701838045978</v>
+        <f t="shared" si="44"/>
+        <v>101.20347881499963</v>
       </c>
       <c r="CD24" s="2">
-        <f t="shared" si="39"/>
-        <v>97.980167461436778</v>
+        <f t="shared" si="44"/>
+        <v>96.143304874249637</v>
       </c>
       <c r="CE24" s="2">
-        <f t="shared" si="39"/>
-        <v>93.081159088364942</v>
+        <f t="shared" si="44"/>
+        <v>91.336139630537147</v>
       </c>
       <c r="CF24" s="2">
-        <f t="shared" si="39"/>
-        <v>88.427101133946692</v>
+        <f t="shared" si="44"/>
+        <v>86.769332649010281</v>
       </c>
       <c r="CG24" s="2">
-        <f t="shared" si="39"/>
-        <v>84.005746077249356</v>
+        <f t="shared" si="44"/>
+        <v>82.430866016559762</v>
       </c>
       <c r="CH24" s="2">
-        <f t="shared" si="39"/>
-        <v>79.805458773386889</v>
+        <f t="shared" si="44"/>
+        <v>78.309322715731767</v>
       </c>
       <c r="CI24" s="2">
-        <f t="shared" si="39"/>
-        <v>75.815185834717539</v>
+        <f t="shared" si="44"/>
+        <v>74.393856579945179</v>
       </c>
       <c r="CJ24" s="2">
-        <f t="shared" si="39"/>
-        <v>72.024426542981658</v>
+        <f t="shared" si="44"/>
+        <v>70.674163750947912</v>
       </c>
       <c r="CK24" s="2">
-        <f t="shared" si="39"/>
-        <v>68.423205215832567</v>
+        <f t="shared" si="44"/>
+        <v>67.140455563400508</v>
       </c>
       <c r="CL24" s="2">
-        <f t="shared" si="39"/>
-        <v>65.00204495504093</v>
+        <f t="shared" si="44"/>
+        <v>63.783432785230481</v>
       </c>
       <c r="CM24" s="2">
-        <f t="shared" si="39"/>
-        <v>61.751942707288883</v>
+        <f t="shared" si="44"/>
+        <v>60.594261145968957</v>
       </c>
       <c r="CN24" s="2">
-        <f t="shared" si="39"/>
-        <v>58.664345571924436</v>
+        <f t="shared" si="44"/>
+        <v>57.564548088670506</v>
       </c>
       <c r="CO24" s="2">
-        <f t="shared" si="39"/>
-        <v>55.731128293328211</v>
+        <f t="shared" si="44"/>
+        <v>54.686320684236975</v>
       </c>
       <c r="CP24" s="2">
-        <f t="shared" si="39"/>
-        <v>52.944571878661797</v>
+        <f t="shared" si="44"/>
+        <v>51.952004650025124</v>
       </c>
       <c r="CQ24" s="2">
-        <f t="shared" si="39"/>
-        <v>50.297343284728704</v>
+        <f t="shared" si="44"/>
+        <v>49.354404417523867</v>
       </c>
       <c r="CR24" s="2">
-        <f t="shared" si="39"/>
-        <v>47.782476120492269</v>
+        <f t="shared" si="44"/>
+        <v>46.886684196647671</v>
       </c>
       <c r="CS24" s="2">
-        <f t="shared" si="39"/>
-        <v>45.393352314467656</v>
+        <f t="shared" si="44"/>
+        <v>44.542349986815289</v>
       </c>
       <c r="CT24" s="2">
-        <f t="shared" si="39"/>
-        <v>43.12368469874427</v>
+        <f t="shared" si="44"/>
+        <v>42.315232487474525</v>
       </c>
       <c r="CU24" s="2">
-        <f t="shared" si="39"/>
-        <v>40.967500463807056</v>
+        <f t="shared" si="44"/>
+        <v>40.1994708631008</v>
       </c>
       <c r="CV24" s="2">
-        <f t="shared" si="39"/>
-        <v>38.919125440616703</v>
+        <f t="shared" si="44"/>
+        <v>38.189497319945758</v>
       </c>
       <c r="CW24" s="2">
-        <f t="shared" si="39"/>
-        <v>36.973169168585869</v>
+        <f t="shared" si="44"/>
+        <v>36.280022453948469</v>
       </c>
       <c r="CX24" s="2">
-        <f t="shared" si="39"/>
-        <v>35.124510710156571</v>
+        <f t="shared" si="44"/>
+        <v>34.466021331251042</v>
       </c>
       <c r="CY24" s="2">
-        <f t="shared" si="39"/>
-        <v>33.36828517464874</v>
+        <f t="shared" si="44"/>
+        <v>32.742720264688487</v>
       </c>
       <c r="CZ24" s="2">
-        <f t="shared" si="39"/>
-        <v>31.6998709159163</v>
+        <f t="shared" si="44"/>
+        <v>31.105584251454061</v>
       </c>
       <c r="DA24" s="2">
-        <f t="shared" si="39"/>
-        <v>30.114877370120485</v>
+        <f t="shared" si="44"/>
+        <v>29.550305038881358</v>
       </c>
       <c r="DB24" s="2">
-        <f t="shared" si="39"/>
-        <v>28.609133501614458</v>
+        <f t="shared" si="44"/>
+        <v>28.072789786937289</v>
       </c>
       <c r="DC24" s="2">
-        <f t="shared" si="39"/>
-        <v>27.178676826533735</v>
+        <f t="shared" si="44"/>
+        <v>26.669150297590424</v>
       </c>
       <c r="DD24" s="2">
-        <f t="shared" si="39"/>
-        <v>25.819742985207046</v>
+        <f t="shared" si="44"/>
+        <v>25.3356927827109</v>
       </c>
       <c r="DE24" s="2">
-        <f t="shared" si="39"/>
-        <v>24.528755835946694</v>
+        <f t="shared" si="44"/>
+        <v>24.068908143575353</v>
       </c>
       <c r="DF24" s="2">
-        <f t="shared" ref="DF24:EI24" si="40">+DE24*(1+$AU$30)</f>
-        <v>23.302318044149359</v>
+        <f t="shared" si="44"/>
+        <v>22.865462736396584</v>
       </c>
       <c r="DG24" s="2">
-        <f t="shared" si="40"/>
-        <v>22.137202141941891</v>
+        <f t="shared" si="44"/>
+        <v>21.722189599576755</v>
       </c>
       <c r="DH24" s="2">
-        <f t="shared" si="40"/>
-        <v>21.030342034844796</v>
+        <f t="shared" si="44"/>
+        <v>20.636080119597917</v>
       </c>
       <c r="DI24" s="2">
-        <f t="shared" si="40"/>
-        <v>19.978824933102555</v>
+        <f t="shared" si="44"/>
+        <v>19.60427611361802</v>
       </c>
       <c r="DJ24" s="2">
-        <f t="shared" si="40"/>
-        <v>18.979883686447426</v>
+        <f t="shared" ref="DJ24:EM24" si="45">+DI24*(1+$AY$30)</f>
+        <v>18.62406230793712</v>
       </c>
       <c r="DK24" s="2">
-        <f t="shared" si="40"/>
-        <v>18.030889502125053</v>
+        <f t="shared" si="45"/>
+        <v>17.692859192540261</v>
       </c>
       <c r="DL24" s="2">
-        <f t="shared" si="40"/>
-        <v>17.1293450270188</v>
+        <f t="shared" si="45"/>
+        <v>16.808216232913246</v>
       </c>
       <c r="DM24" s="2">
-        <f t="shared" si="40"/>
-        <v>16.272877775667858</v>
+        <f t="shared" si="45"/>
+        <v>15.967805421267583</v>
       </c>
       <c r="DN24" s="2">
-        <f t="shared" si="40"/>
-        <v>15.459233886884464</v>
+        <f t="shared" si="45"/>
+        <v>15.169415150204204</v>
       </c>
       <c r="DO24" s="2">
-        <f t="shared" si="40"/>
-        <v>14.68627219254024</v>
+        <f t="shared" si="45"/>
+        <v>14.410944392693994</v>
       </c>
       <c r="DP24" s="2">
-        <f t="shared" si="40"/>
-        <v>13.951958582913228</v>
+        <f t="shared" si="45"/>
+        <v>13.690397173059294</v>
       </c>
       <c r="DQ24" s="2">
-        <f t="shared" si="40"/>
-        <v>13.254360653767566</v>
+        <f t="shared" si="45"/>
+        <v>13.005877314406328</v>
       </c>
       <c r="DR24" s="2">
-        <f t="shared" si="40"/>
-        <v>12.591642621079188</v>
+        <f t="shared" si="45"/>
+        <v>12.355583448686012</v>
       </c>
       <c r="DS24" s="2">
-        <f t="shared" si="40"/>
-        <v>11.962060490025229</v>
+        <f t="shared" si="45"/>
+        <v>11.73780427625171</v>
       </c>
       <c r="DT24" s="2">
-        <f t="shared" si="40"/>
-        <v>11.363957465523967</v>
+        <f t="shared" si="45"/>
+        <v>11.150914062439124</v>
       </c>
       <c r="DU24" s="2">
-        <f t="shared" si="40"/>
-        <v>10.795759592247768</v>
+        <f t="shared" si="45"/>
+        <v>10.593368359317168</v>
       </c>
       <c r="DV24" s="2">
-        <f t="shared" si="40"/>
-        <v>10.255971612635379</v>
+        <f t="shared" si="45"/>
+        <v>10.06369994135131</v>
       </c>
       <c r="DW24" s="2">
-        <f t="shared" si="40"/>
-        <v>9.7431730320036092</v>
+        <f t="shared" si="45"/>
+        <v>9.560514944283744</v>
       </c>
       <c r="DX24" s="2">
-        <f t="shared" si="40"/>
-        <v>9.2560143804034283</v>
+        <f t="shared" si="45"/>
+        <v>9.082489197069556</v>
       </c>
       <c r="DY24" s="2">
-        <f t="shared" si="40"/>
-        <v>8.7932136613832572</v>
+        <f t="shared" si="45"/>
+        <v>8.6283647372160779</v>
       </c>
       <c r="DZ24" s="2">
-        <f t="shared" si="40"/>
-        <v>8.3535529783140934</v>
+        <f t="shared" si="45"/>
+        <v>8.1969465003552742</v>
       </c>
       <c r="EA24" s="2">
-        <f t="shared" si="40"/>
-        <v>7.9358753293983879</v>
+        <f t="shared" si="45"/>
+        <v>7.7870991753375103</v>
       </c>
       <c r="EB24" s="2">
-        <f t="shared" si="40"/>
-        <v>7.5390815629284678</v>
+        <f t="shared" si="45"/>
+        <v>7.3977442165706346</v>
       </c>
       <c r="EC24" s="2">
-        <f t="shared" si="40"/>
-        <v>7.1621274847820438</v>
+        <f t="shared" si="45"/>
+        <v>7.0278570057421028</v>
       </c>
       <c r="ED24" s="2">
-        <f t="shared" si="40"/>
-        <v>6.8040211105429416</v>
+        <f t="shared" si="45"/>
+        <v>6.6764641554549975</v>
       </c>
       <c r="EE24" s="2">
-        <f t="shared" si="40"/>
-        <v>6.4638200550157938</v>
+        <f t="shared" si="45"/>
+        <v>6.3426409476822476</v>
       </c>
       <c r="EF24" s="2">
-        <f t="shared" si="40"/>
-        <v>6.1406290522650036</v>
+        <f t="shared" si="45"/>
+        <v>6.025508900298135</v>
       </c>
       <c r="EG24" s="2">
-        <f t="shared" si="40"/>
-        <v>5.8335975996517533</v>
+        <f t="shared" si="45"/>
+        <v>5.7242334552832279</v>
       </c>
       <c r="EH24" s="2">
-        <f t="shared" si="40"/>
-        <v>5.5419177196691658</v>
+        <f t="shared" si="45"/>
+        <v>5.4380217825190664</v>
       </c>
       <c r="EI24" s="2">
-        <f t="shared" si="40"/>
-        <v>5.2648218336857076</v>
-      </c>
-    </row>
-    <row r="25" spans="2:139" x14ac:dyDescent="0.25">
+        <f t="shared" si="45"/>
+        <v>5.166120693393113</v>
+      </c>
+      <c r="EJ24" s="2">
+        <f t="shared" si="45"/>
+        <v>4.9078146587234572</v>
+      </c>
+      <c r="EK24" s="2">
+        <f t="shared" si="45"/>
+        <v>4.6624239257872846</v>
+      </c>
+      <c r="EL24" s="2">
+        <f t="shared" si="45"/>
+        <v>4.4293027294979206</v>
+      </c>
+      <c r="EM24" s="2">
+        <f t="shared" si="45"/>
+        <v>4.2078375930230241</v>
+      </c>
+    </row>
+    <row r="25" spans="2:143" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
         <v>27</v>
       </c>
       <c r="E25" s="6">
-        <f t="shared" ref="E25:L25" si="41">+E24/E26</f>
+        <f t="shared" ref="E25:L25" si="46">+E24/E26</f>
         <v>-0.58987341772151902</v>
       </c>
       <c r="F25" s="6">
-        <f t="shared" si="41"/>
+        <f t="shared" si="46"/>
         <v>-0.68513853904282118</v>
       </c>
       <c r="G25" s="6">
-        <f t="shared" si="41"/>
+        <f t="shared" si="46"/>
         <v>2.8395348837209302</v>
       </c>
       <c r="H25" s="6">
-        <f t="shared" si="41"/>
+        <f t="shared" si="46"/>
         <v>6.4501160092807428</v>
       </c>
       <c r="I25" s="6">
-        <f t="shared" si="41"/>
+        <f t="shared" si="46"/>
         <v>7.6797235023041477</v>
       </c>
       <c r="J25" s="6">
-        <f t="shared" si="41"/>
+        <f t="shared" si="46"/>
         <v>11.294663573085847</v>
       </c>
       <c r="K25" s="6">
-        <f t="shared" si="41"/>
+        <f t="shared" si="46"/>
         <v>8.5845070422535219</v>
       </c>
       <c r="L25" s="6">
-        <f t="shared" si="41"/>
+        <f t="shared" si="46"/>
         <v>5.2434367541766109</v>
       </c>
       <c r="M25" s="6">
-        <f t="shared" ref="M25:S25" si="42">+M24/M26</f>
+        <f t="shared" ref="M25:S25" si="47">+M24/M26</f>
         <v>2.5315533980582523</v>
       </c>
       <c r="N25" s="6">
-        <f t="shared" si="42"/>
+        <f t="shared" si="47"/>
         <v>3.617283950617284</v>
       </c>
       <c r="O25" s="6">
-        <f t="shared" si="42"/>
+        <f t="shared" si="47"/>
         <v>0.19506172839506172</v>
       </c>
       <c r="P25" s="6">
-        <f t="shared" si="42"/>
+        <f t="shared" si="47"/>
         <v>-3.622047244094488</v>
       </c>
       <c r="Q25" s="6">
-        <f t="shared" si="42"/>
+        <f t="shared" si="47"/>
         <v>-9.5275590551181111</v>
       </c>
       <c r="R25" s="6">
-        <f t="shared" si="42"/>
+        <f t="shared" si="47"/>
         <v>0.54936708860759498</v>
       </c>
       <c r="S25" s="6">
-        <f t="shared" si="42"/>
+        <f t="shared" si="47"/>
         <v>-3.075916230366492</v>
       </c>
       <c r="T25" s="6">
@@ -4278,52 +4502,84 @@
         <f>+V24/V26</f>
         <v>-2.9090909090909092</v>
       </c>
-      <c r="AH25" s="20">
-        <f>+AH24/AH26</f>
-        <v>1.8157935483870964</v>
-      </c>
-      <c r="AI25" s="20">
-        <f t="shared" ref="AI25:AR25" si="43">+AI24/AI26</f>
-        <v>3.5937290322580639</v>
-      </c>
-      <c r="AJ25" s="20">
-        <f t="shared" si="43"/>
-        <v>2.9563664516129027</v>
-      </c>
-      <c r="AK25" s="20">
-        <f t="shared" si="43"/>
-        <v>2.6313445161290323</v>
+      <c r="W25" s="6">
+        <f t="shared" ref="W25:AD25" si="48">+W24/W26</f>
+        <v>-2.5051813471502591</v>
+      </c>
+      <c r="X25" s="6">
+        <f t="shared" si="48"/>
+        <v>-1.9123711340206186</v>
+      </c>
+      <c r="Y25" s="6">
+        <f t="shared" si="48"/>
+        <v>-0.51282051282051277</v>
+      </c>
+      <c r="Z25" s="6" t="e">
+        <f t="shared" si="48"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AA25" s="6" t="e">
+        <f t="shared" si="48"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AB25" s="6" t="e">
+        <f t="shared" si="48"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AC25" s="6" t="e">
+        <f t="shared" si="48"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AD25" s="6" t="e">
+        <f t="shared" si="48"/>
+        <v>#DIV/0!</v>
       </c>
       <c r="AL25" s="20">
-        <f t="shared" si="43"/>
-        <v>2.3868975483870964</v>
+        <f>+AL24/AL26</f>
+        <v>1.6346322580645156</v>
       </c>
       <c r="AM25" s="20">
-        <f t="shared" si="43"/>
-        <v>2.2065853099354844</v>
+        <f t="shared" ref="AM25:AV25" si="49">+AM24/AM26</f>
+        <v>3.3247741935483868</v>
       </c>
       <c r="AN25" s="20">
-        <f t="shared" si="43"/>
-        <v>2.0730586529961292</v>
+        <f t="shared" si="49"/>
+        <v>2.6995633548387103</v>
       </c>
       <c r="AO25" s="20">
-        <f t="shared" si="43"/>
-        <v>1.9617365887906066</v>
+        <f t="shared" si="49"/>
+        <v>2.3489280000000003</v>
       </c>
       <c r="AP25" s="20">
-        <f t="shared" si="43"/>
-        <v>1.8785170193639322</v>
+        <f t="shared" si="49"/>
+        <v>2.0982351483870967</v>
       </c>
       <c r="AQ25" s="20">
-        <f t="shared" si="43"/>
-        <v>1.8179449972669908</v>
+        <f t="shared" si="49"/>
+        <v>1.9060062317419355</v>
       </c>
       <c r="AR25" s="20">
-        <f t="shared" si="43"/>
-        <v>1.7756994884187935</v>
-      </c>
-    </row>
-    <row r="26" spans="2:139" x14ac:dyDescent="0.25">
+        <f t="shared" si="49"/>
+        <v>1.7559410930477424</v>
+      </c>
+      <c r="AS25" s="20">
+        <f t="shared" si="49"/>
+        <v>1.6376590375441546</v>
+      </c>
+      <c r="AT25" s="20">
+        <f t="shared" si="49"/>
+        <v>1.5454023106872867</v>
+      </c>
+      <c r="AU25" s="20">
+        <f t="shared" si="49"/>
+        <v>1.4739625249651322</v>
+      </c>
+      <c r="AV25" s="20">
+        <f t="shared" si="49"/>
+        <v>1.4192037826377082</v>
+      </c>
+    </row>
+    <row r="26" spans="2:143" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
         <v>1</v>
       </c>
@@ -4381,52 +4637,61 @@
       <c r="V26" s="1">
         <v>385</v>
       </c>
-      <c r="AH26" s="2">
+      <c r="W26" s="1">
+        <v>386</v>
+      </c>
+      <c r="X26" s="1">
+        <v>388</v>
+      </c>
+      <c r="Y26" s="1">
+        <v>390</v>
+      </c>
+      <c r="AL26" s="2">
         <f>AVERAGE(S26:V26)</f>
         <v>387.5</v>
       </c>
-      <c r="AI26" s="2">
-        <f>+AH26</f>
+      <c r="AM26" s="2">
+        <f>+AL26</f>
         <v>387.5</v>
       </c>
-      <c r="AJ26" s="2">
-        <f>+AI26</f>
+      <c r="AN26" s="2">
+        <f>+AM26</f>
         <v>387.5</v>
       </c>
-      <c r="AK26" s="2">
-        <f t="shared" ref="AK26:AR26" si="44">+AJ26</f>
+      <c r="AO26" s="2">
+        <f t="shared" ref="AO26:AV26" si="50">+AN26</f>
         <v>387.5</v>
       </c>
-      <c r="AL26" s="2">
-        <f t="shared" si="44"/>
+      <c r="AP26" s="2">
+        <f t="shared" si="50"/>
         <v>387.5</v>
       </c>
-      <c r="AM26" s="2">
-        <f t="shared" si="44"/>
+      <c r="AQ26" s="2">
+        <f t="shared" si="50"/>
         <v>387.5</v>
       </c>
-      <c r="AN26" s="2">
-        <f t="shared" si="44"/>
+      <c r="AR26" s="2">
+        <f t="shared" si="50"/>
         <v>387.5</v>
       </c>
-      <c r="AO26" s="2">
-        <f t="shared" si="44"/>
+      <c r="AS26" s="2">
+        <f t="shared" si="50"/>
         <v>387.5</v>
       </c>
-      <c r="AP26" s="2">
-        <f t="shared" si="44"/>
+      <c r="AT26" s="2">
+        <f t="shared" si="50"/>
         <v>387.5</v>
       </c>
-      <c r="AQ26" s="2">
-        <f t="shared" si="44"/>
+      <c r="AU26" s="2">
+        <f t="shared" si="50"/>
         <v>387.5</v>
       </c>
-      <c r="AR26" s="2">
-        <f t="shared" si="44"/>
+      <c r="AV26" s="2">
+        <f t="shared" si="50"/>
         <v>387.5</v>
       </c>
     </row>
-    <row r="28" spans="2:139" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:143" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
         <v>106</v>
       </c>
@@ -4435,81 +4700,113 @@
         <v>1</v>
       </c>
       <c r="F28" s="17">
-        <f t="shared" ref="F28:R28" si="45">F16/F14</f>
+        <f t="shared" ref="F28:R28" si="51">F16/F14</f>
         <v>0.98598949211908937</v>
       </c>
       <c r="G28" s="17">
-        <f t="shared" si="45"/>
+        <f t="shared" si="51"/>
         <v>0.90036138358286011</v>
       </c>
       <c r="H28" s="17">
-        <f t="shared" si="45"/>
+        <f t="shared" si="51"/>
         <v>0.82774460266421679</v>
       </c>
       <c r="I28" s="17">
-        <f t="shared" si="45"/>
+        <f t="shared" si="51"/>
         <v>0.85469913463473535</v>
       </c>
       <c r="J28" s="17">
-        <f t="shared" si="45"/>
+        <f t="shared" si="51"/>
         <v>0.86797947580085977</v>
       </c>
       <c r="K28" s="17">
-        <f t="shared" si="45"/>
+        <f t="shared" si="51"/>
         <v>0.83234421364985167</v>
       </c>
       <c r="L28" s="17">
-        <f t="shared" si="45"/>
+        <f t="shared" si="51"/>
         <v>0.7092019372499474</v>
       </c>
       <c r="M28" s="17">
-        <f t="shared" si="45"/>
+        <f t="shared" si="51"/>
         <v>0.67300832342449468</v>
       </c>
       <c r="N28" s="17">
-        <f t="shared" si="45"/>
+        <f t="shared" si="51"/>
         <v>0.62273800157356407</v>
       </c>
       <c r="O28" s="17">
-        <f t="shared" si="45"/>
+        <f t="shared" si="51"/>
         <v>0.57465091299677762</v>
       </c>
       <c r="P28" s="17">
-        <f t="shared" si="45"/>
+        <f t="shared" si="51"/>
         <v>-1.125</v>
       </c>
       <c r="Q28" s="17">
-        <f t="shared" si="45"/>
+        <f t="shared" si="51"/>
         <v>-0.2239213544511196</v>
       </c>
       <c r="R28" s="17">
-        <f t="shared" si="45"/>
+        <f t="shared" si="51"/>
         <v>0.66951262895766628</v>
       </c>
       <c r="S28" s="17">
-        <f t="shared" ref="S28:V28" si="46">S16/S14</f>
+        <f t="shared" ref="S28:V28" si="52">S16/S14</f>
         <v>0.42514970059880242</v>
       </c>
       <c r="T28" s="17">
-        <f t="shared" si="46"/>
+        <f t="shared" si="52"/>
         <v>0.52282157676348551</v>
       </c>
       <c r="U28" s="17">
-        <f t="shared" si="46"/>
+        <f t="shared" si="52"/>
         <v>0.72395273899033297</v>
       </c>
       <c r="V28" s="17">
-        <f t="shared" si="46"/>
+        <f t="shared" si="52"/>
         <v>0.2349896480331263</v>
       </c>
-      <c r="AT28" t="s">
-        <v>156</v>
-      </c>
-      <c r="AU28" s="18">
+      <c r="W28" s="17">
+        <f t="shared" ref="W28:AD28" si="53">W16/W14</f>
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="X28" s="17">
+        <f t="shared" si="53"/>
+        <v>0.80281690140845074</v>
+      </c>
+      <c r="Y28" s="17">
+        <f t="shared" si="53"/>
+        <v>0.79625984251968507</v>
+      </c>
+      <c r="Z28" s="17">
+        <f t="shared" si="53"/>
+        <v>0</v>
+      </c>
+      <c r="AA28" s="17">
+        <f t="shared" si="53"/>
+        <v>-1.455012853470437</v>
+      </c>
+      <c r="AB28" s="17" t="e">
+        <f t="shared" si="53"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AC28" s="17" t="e">
+        <f t="shared" si="53"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AD28" s="17" t="e">
+        <f t="shared" si="53"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AX28" t="s">
+        <v>155</v>
+      </c>
+      <c r="AY28" s="18">
         <v>0.09</v>
       </c>
     </row>
-    <row r="29" spans="2:139" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:143" x14ac:dyDescent="0.25">
       <c r="B29" s="18" t="s">
         <v>107</v>
       </c>
@@ -4518,98 +4815,130 @@
         <v>-4.3103448275862068E-3</v>
       </c>
       <c r="F29" s="17">
-        <f t="shared" ref="F29:R29" si="47">F23/F22</f>
+        <f t="shared" ref="F29:R29" si="54">F23/F22</f>
         <v>-3.6900369003690036E-3</v>
       </c>
       <c r="G29" s="17">
-        <f t="shared" si="47"/>
+        <f t="shared" si="54"/>
         <v>3.0952380952380953E-2</v>
       </c>
       <c r="H29" s="17">
-        <f t="shared" si="47"/>
+        <f t="shared" si="54"/>
         <v>9.2393078681031665E-2</v>
       </c>
       <c r="I29" s="17">
-        <f t="shared" si="47"/>
+        <f t="shared" si="54"/>
         <v>6.1655405405405407E-2</v>
       </c>
       <c r="J29" s="17">
-        <f t="shared" si="47"/>
+        <f t="shared" si="54"/>
         <v>0.10018484288354898</v>
       </c>
       <c r="K29" s="17">
-        <f t="shared" si="47"/>
+        <f t="shared" si="54"/>
         <v>0.13525656183494916</v>
       </c>
       <c r="L29" s="17">
-        <f t="shared" si="47"/>
+        <f t="shared" si="54"/>
         <v>0.11196443007275667</v>
       </c>
       <c r="M29" s="17">
-        <f t="shared" si="47"/>
+        <f t="shared" si="54"/>
         <v>0.142974527526705</v>
       </c>
       <c r="N29" s="17">
-        <f t="shared" si="47"/>
+        <f t="shared" si="54"/>
         <v>0.11480362537764351</v>
       </c>
       <c r="O29" s="17">
-        <f t="shared" si="47"/>
+        <f t="shared" si="54"/>
         <v>1.2590163934426231</v>
       </c>
       <c r="P29" s="17">
-        <f t="shared" si="47"/>
+        <f t="shared" si="54"/>
         <v>0.21097770154373929</v>
       </c>
       <c r="Q29" s="17">
-        <f t="shared" si="47"/>
+        <f t="shared" si="54"/>
         <v>-0.8539325842696629</v>
       </c>
       <c r="R29" s="17">
-        <f t="shared" si="47"/>
+        <f t="shared" si="54"/>
         <v>-2.1</v>
       </c>
       <c r="S29" s="17">
-        <f t="shared" ref="S29:V29" si="48">S23/S22</f>
+        <f t="shared" ref="S29:V29" si="55">S23/S22</f>
         <v>-8.5836909871244635E-3</v>
       </c>
       <c r="T29" s="17">
-        <f t="shared" si="48"/>
+        <f t="shared" si="55"/>
         <v>0</v>
       </c>
       <c r="U29" s="17">
-        <f t="shared" si="48"/>
+        <f t="shared" si="55"/>
         <v>0.38095238095238093</v>
       </c>
       <c r="V29" s="17">
-        <f t="shared" si="48"/>
+        <f t="shared" si="55"/>
         <v>5.4054054054054057E-2</v>
       </c>
-      <c r="AT29" t="s">
+      <c r="W29" s="17">
+        <f t="shared" ref="W29:AD29" si="56">W23/W22</f>
+        <v>-7.2916666666666668E-3</v>
+      </c>
+      <c r="X29" s="17">
+        <f t="shared" si="56"/>
+        <v>-9.5238095238095247E-3</v>
+      </c>
+      <c r="Y29" s="17">
+        <f t="shared" si="56"/>
+        <v>-6.9518716577540107E-2</v>
+      </c>
+      <c r="Z29" s="17" t="e">
+        <f t="shared" si="56"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AA29" s="17">
+        <f t="shared" si="56"/>
+        <v>0</v>
+      </c>
+      <c r="AB29" s="17" t="e">
+        <f t="shared" si="56"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AC29" s="17" t="e">
+        <f t="shared" si="56"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AD29" s="17" t="e">
+        <f t="shared" si="56"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AX29" t="s">
+        <v>156</v>
+      </c>
+      <c r="AY29" s="18">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="30" spans="2:143" x14ac:dyDescent="0.25">
+      <c r="AX30" t="s">
         <v>157</v>
       </c>
-      <c r="AU29" s="18">
-        <v>0.01</v>
-      </c>
-    </row>
-    <row r="30" spans="2:139" x14ac:dyDescent="0.25">
-      <c r="AT30" t="s">
+      <c r="AY30" s="18">
+        <v>-0.05</v>
+      </c>
+    </row>
+    <row r="31" spans="2:143" x14ac:dyDescent="0.25">
+      <c r="AX31" t="s">
         <v>158</v>
       </c>
-      <c r="AU30" s="18">
-        <v>-0.05</v>
-      </c>
-    </row>
-    <row r="31" spans="2:139" x14ac:dyDescent="0.25">
-      <c r="AT31" t="s">
-        <v>159</v>
-      </c>
-      <c r="AU31" s="2">
-        <f>NPV(AU28,AH24:EI24)+Main!K5</f>
-        <v>17584.312106225829</v>
-      </c>
-    </row>
-    <row r="32" spans="2:139" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AY31" s="2">
+        <f>NPV(AY28,AL24:EM24)+Main!K5</f>
+        <v>13459.883759215365</v>
+      </c>
+    </row>
+    <row r="32" spans="2:143" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B32" s="2" t="s">
         <v>3</v>
       </c>
@@ -4646,12 +4975,12 @@
         <f>1927+5098+2494</f>
         <v>9519</v>
       </c>
-      <c r="AT32" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="AU32" s="20">
-        <f>+AU31/Main!K3</f>
-        <v>45.695161719595738</v>
+      <c r="AX32" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="AY32" s="20">
+        <f>+AY31/Main!K3</f>
+        <v>33.922252734098251</v>
       </c>
     </row>
     <row r="33" spans="2:22" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -5148,7 +5477,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="2:33" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:37" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B49" s="2" t="s">
         <v>108</v>
       </c>
@@ -5180,7 +5509,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="50" spans="2:33" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:37" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B50" s="2" t="s">
         <v>52</v>
       </c>
@@ -5212,7 +5541,7 @@
         <v>10901</v>
       </c>
     </row>
-    <row r="51" spans="2:33" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:37" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B51" s="2" t="s">
         <v>53</v>
       </c>
@@ -5250,7 +5579,7 @@
         <v>14142</v>
       </c>
     </row>
-    <row r="54" spans="2:33" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:37" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B54" s="2" t="s">
         <v>98</v>
       </c>
@@ -5273,9 +5602,9 @@
       </c>
       <c r="N54" s="3"/>
     </row>
-    <row r="57" spans="2:33" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:37" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B57" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C57" s="3"/>
       <c r="D57" s="3"/>
@@ -5289,31 +5618,31 @@
       <c r="L57" s="3"/>
       <c r="M57" s="3"/>
       <c r="N57" s="3"/>
-      <c r="AF57" s="2">
+      <c r="AJ57" s="2">
         <v>-3118</v>
       </c>
-      <c r="AG57" s="2">
+      <c r="AK57" s="2">
         <v>-3004</v>
       </c>
     </row>
-    <row r="58" spans="2:33" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:37" x14ac:dyDescent="0.25">
       <c r="B58" t="s">
-        <v>155</v>
-      </c>
-      <c r="AF58" s="2">
+        <v>154</v>
+      </c>
+      <c r="AJ58" s="2">
         <v>-707</v>
       </c>
-      <c r="AG58" s="2">
+      <c r="AK58" s="2">
         <v>-1051</v>
       </c>
     </row>
-    <row r="59" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="AF59" s="2">
-        <f>+AF57+AF58</f>
+    <row r="59" spans="2:37" x14ac:dyDescent="0.25">
+      <c r="AJ59" s="2">
+        <f>+AJ57+AJ58</f>
         <v>-3825</v>
       </c>
-      <c r="AG59" s="2">
-        <f>+AG57+AG58</f>
+      <c r="AK59" s="2">
+        <f>+AK57+AK58</f>
         <v>-4055</v>
       </c>
     </row>
